--- a/Notes/datamapping-MOVES.xlsx
+++ b/Notes/datamapping-MOVES.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4129" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="1018">
   <si>
     <t>Fake Out</t>
   </si>
@@ -2870,9 +2870,6 @@
     <t>switchturn, defensedown, switchturn</t>
   </si>
   <si>
-    <t>switchturn, attackdown, switchturn</t>
-  </si>
-  <si>
     <t>EFFECT_LEECH_HIT</t>
   </si>
   <si>
@@ -2964,6 +2961,99 @@
   </si>
   <si>
     <t>STRUGGLE  $FF</t>
+  </si>
+  <si>
+    <t>was field move</t>
+  </si>
+  <si>
+    <t>add to egg moves?</t>
+  </si>
+  <si>
+    <t>fissure?</t>
+  </si>
+  <si>
+    <t>porygon battle_tower parties</t>
+  </si>
+  <si>
+    <t>replace low_kick</t>
+  </si>
+  <si>
+    <t>LOW_SWEEP</t>
+  </si>
+  <si>
+    <t>oSPEEDdown</t>
+  </si>
+  <si>
+    <t>miss damage</t>
+  </si>
+  <si>
+    <t>tutor?</t>
+  </si>
+  <si>
+    <t>tutor? (if kept)</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>tx</t>
+  </si>
+  <si>
+    <t>CRUSH_CLAW</t>
+  </si>
+  <si>
+    <t>oDEFdown</t>
+  </si>
+  <si>
+    <t>EFFECT_DEFENSE_DOWN_HIT</t>
+  </si>
+  <si>
+    <t>50+</t>
+  </si>
+  <si>
+    <t>bugsy TM x-scissor</t>
+  </si>
+  <si>
+    <t>fire_fang</t>
+  </si>
+  <si>
+    <t>ice_fang</t>
+  </si>
+  <si>
+    <t>thunder_fang</t>
+  </si>
+  <si>
+    <t>gyro_ball</t>
+  </si>
+  <si>
+    <t>icicle_spear</t>
+  </si>
+  <si>
+    <t>seed_bomb</t>
+  </si>
+  <si>
+    <t>low_sweep</t>
+  </si>
+  <si>
+    <t>crush_claw</t>
+  </si>
+  <si>
+    <t>fury_strikes</t>
+  </si>
+  <si>
+    <t>data\battle\ai\encore_moves.asm, stall_moves.asm</t>
+  </si>
+  <si>
+    <t>bulk_up</t>
+  </si>
+  <si>
+    <t>calm_mind</t>
+  </si>
+  <si>
+    <t>rep</t>
+  </si>
+  <si>
+    <t>conversion3</t>
   </si>
 </sst>
 </file>
@@ -3064,7 +3154,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3230,6 +3320,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3451,7 +3547,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3693,21 +3789,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="170">
+  <dxfs count="280">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -3787,599 +3907,605 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4970,136 +5096,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <color rgb="FF00B050"/>
@@ -5172,6 +5168,1182 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5407,21 +6579,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A7C0DFF-4CF3-4444-A522-D1A1933B3902}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" dataDxfId="168" headerRowBorderDxfId="169" tableBorderDxfId="167">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A7C0DFF-4CF3-4444-A522-D1A1933B3902}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" dataDxfId="278" headerRowBorderDxfId="279" tableBorderDxfId="277">
   <autoFilter ref="A1:I1048576" xr:uid="{2A7C0DFF-4CF3-4444-A522-D1A1933B3902}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I217">
     <sortCondition ref="H1:H1048576"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{AFB094CB-7242-4567-944A-EFFFE8B3A24F}" name="Column1" dataDxfId="166"/>
-    <tableColumn id="2" xr3:uid="{3C636B82-4CB2-4387-9FC1-0265760045DD}" name="Column2" dataDxfId="165"/>
-    <tableColumn id="3" xr3:uid="{E008ED4E-55D3-4247-9E09-60303385AEC9}" name="Column3" dataDxfId="164"/>
-    <tableColumn id="4" xr3:uid="{73B7BD88-7986-4FE0-8855-71D995327508}" name="Column4" dataDxfId="163"/>
-    <tableColumn id="5" xr3:uid="{B3EAF442-3D05-41A2-9223-67D9C2752786}" name="Column5" dataDxfId="162"/>
-    <tableColumn id="6" xr3:uid="{09BFB138-6570-4FEE-9CE6-29681496F527}" name="Column6" dataDxfId="161"/>
-    <tableColumn id="7" xr3:uid="{377F5855-821F-467F-8869-9DE5CAA86201}" name="Column7" dataDxfId="160"/>
-    <tableColumn id="8" xr3:uid="{B15E4D57-A46C-4A6E-98A5-CBF597B47545}" name="Column8" dataDxfId="159"/>
-    <tableColumn id="9" xr3:uid="{BD5E734E-3897-44EE-9F16-54CB29D86410}" name="Column9" dataDxfId="158"/>
+    <tableColumn id="1" xr3:uid="{AFB094CB-7242-4567-944A-EFFFE8B3A24F}" name="Column1" dataDxfId="276"/>
+    <tableColumn id="2" xr3:uid="{3C636B82-4CB2-4387-9FC1-0265760045DD}" name="Column2" dataDxfId="275"/>
+    <tableColumn id="3" xr3:uid="{E008ED4E-55D3-4247-9E09-60303385AEC9}" name="Column3" dataDxfId="274"/>
+    <tableColumn id="4" xr3:uid="{73B7BD88-7986-4FE0-8855-71D995327508}" name="Column4" dataDxfId="273"/>
+    <tableColumn id="5" xr3:uid="{B3EAF442-3D05-41A2-9223-67D9C2752786}" name="Column5" dataDxfId="272"/>
+    <tableColumn id="6" xr3:uid="{09BFB138-6570-4FEE-9CE6-29681496F527}" name="Column6" dataDxfId="271"/>
+    <tableColumn id="7" xr3:uid="{377F5855-821F-467F-8869-9DE5CAA86201}" name="Column7" dataDxfId="270"/>
+    <tableColumn id="8" xr3:uid="{B15E4D57-A46C-4A6E-98A5-CBF597B47545}" name="Column8" dataDxfId="269"/>
+    <tableColumn id="9" xr3:uid="{BD5E734E-3897-44EE-9F16-54CB29D86410}" name="Column9" dataDxfId="268"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7603,44 +8775,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C35 M1:M1048576 C1:C17 C24:C25 C20 C30 C43:C1048576 C37:C38">
-    <cfRule type="duplicateValues" dxfId="7" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C35 M1:M1048576 C1:C18 C24:C25 C20 C30 C43:C1048576 C37:C38">
-    <cfRule type="duplicateValues" dxfId="6" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C1048576 C1:C31 C33:C38">
-    <cfRule type="duplicateValues" dxfId="5" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C1048576 M1:M1048576 C1:C31 C33:C38">
-    <cfRule type="duplicateValues" dxfId="4" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576 A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576 C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Notes/datamapping-MOVES.xlsx
+++ b/Notes/datamapping-MOVES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49512027-EB7B-4A91-BA1C-BBBEBE64B99F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318E2B62-4B8F-42A0-984C-60D7B6DA38FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1982F562-5184-46C6-89BD-68E4E108BC42}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4742" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4767" uniqueCount="1398">
   <si>
     <t>bug</t>
   </si>
@@ -3882,15 +3882,9 @@
     <t>HORN_ATTACK, poison</t>
   </si>
   <si>
-    <t>CHARM no heart</t>
-  </si>
-  <si>
     <t>THRASH, fighting</t>
   </si>
   <si>
-    <t>EGG_BOMB, grass</t>
-  </si>
-  <si>
     <t>FURY_ATTACK, ice, w/ crystal hits</t>
   </si>
   <si>
@@ -3903,12 +3897,6 @@
     <t>SAND_ATTACK but SPIKE_CANNON spikes (change?)</t>
   </si>
   <si>
-    <t>PSYBEAM, water</t>
-  </si>
-  <si>
-    <t>WATERFALL, water</t>
-  </si>
-  <si>
     <t>RAPID_SPIN (maybe metal intro)</t>
   </si>
   <si>
@@ -3924,9 +3912,6 @@
     <t>SUPERSONIC, SACRED_FIRE on target</t>
   </si>
   <si>
-    <t>SWEET_SCENT, all gfx are leaves, hit</t>
-  </si>
-  <si>
     <t>SLASH, dark</t>
   </si>
   <si>
@@ -3987,6 +3972,9 @@
     <t>statdown</t>
   </si>
   <si>
+    <t>color</t>
+  </si>
+  <si>
     <t>; aa</t>
   </si>
   <si>
@@ -4219,6 +4207,33 @@
   </si>
   <si>
     <t>EFFECT</t>
+  </si>
+  <si>
+    <t>user doesn't wobble?</t>
+  </si>
+  <si>
+    <t>PSYWAVE, water (psybeam)</t>
+  </si>
+  <si>
+    <t>no endure?</t>
+  </si>
+  <si>
+    <t>hits</t>
+  </si>
+  <si>
+    <t>BARRAGE, green</t>
+  </si>
+  <si>
+    <t>WATERFALL reversed</t>
+  </si>
+  <si>
+    <t>POWDER_SNOW, gfx_reflect, green</t>
+  </si>
+  <si>
+    <t>ACID, ground</t>
+  </si>
+  <si>
+    <t>hex</t>
   </si>
 </sst>
 </file>
@@ -4425,7 +4440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4544,6 +4559,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6531,7 +6547,7 @@
         <v>1268</v>
       </c>
       <c r="J14" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6571,7 +6587,7 @@
         <v>1268</v>
       </c>
       <c r="J16" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6619,7 +6635,7 @@
         <v>1267</v>
       </c>
       <c r="J19" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6648,7 +6664,7 @@
         <v>1268</v>
       </c>
       <c r="J20" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6765,10 +6781,10 @@
         <v>1267</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="J26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -7167,7 +7183,7 @@
         <v>1268</v>
       </c>
       <c r="J50" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7239,11 +7255,11 @@
       <c r="H55" t="s">
         <v>1267</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>1311</v>
+      <c r="I55" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J55" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -7557,7 +7573,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>841</v>
       </c>
@@ -7568,7 +7584,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>842</v>
       </c>
@@ -7579,7 +7595,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>843</v>
       </c>
@@ -7590,7 +7606,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>844</v>
       </c>
@@ -7601,7 +7617,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>845</v>
       </c>
@@ -7612,7 +7628,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>846</v>
       </c>
@@ -7623,7 +7639,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>847</v>
       </c>
@@ -7634,7 +7650,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>848</v>
       </c>
@@ -7645,7 +7661,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>849</v>
       </c>
@@ -7656,7 +7672,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>850</v>
       </c>
@@ -7667,7 +7683,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>851</v>
       </c>
@@ -7678,7 +7694,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>852</v>
       </c>
@@ -7689,7 +7705,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>853</v>
       </c>
@@ -7700,7 +7716,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>854</v>
       </c>
@@ -7711,7 +7727,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>855</v>
       </c>
@@ -7721,8 +7737,11 @@
       <c r="C95" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="I95" s="4" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>856</v>
       </c>
@@ -7755,8 +7774,8 @@
       <c r="H97" t="s">
         <v>1267</v>
       </c>
-      <c r="I97" s="4" t="s">
-        <v>1311</v>
+      <c r="I97" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J97" t="s">
         <v>89</v>
@@ -7839,11 +7858,11 @@
       <c r="H103" t="s">
         <v>1267</v>
       </c>
-      <c r="I103" s="4" t="s">
-        <v>1311</v>
+      <c r="I103" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J103" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -7945,11 +7964,11 @@
       <c r="H111" t="s">
         <v>1267</v>
       </c>
-      <c r="I111" s="4" t="s">
-        <v>1311</v>
+      <c r="I111" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J111" t="s">
-        <v>1280</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -8068,11 +8087,11 @@
       <c r="H120" t="s">
         <v>1267</v>
       </c>
-      <c r="I120" s="4" t="s">
-        <v>1311</v>
+      <c r="I120" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J120" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8109,10 +8128,10 @@
         <v>1267</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="J122" t="s">
-        <v>1282</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8207,7 +8226,7 @@
         <v>1268</v>
       </c>
       <c r="J129" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -8243,11 +8262,11 @@
       <c r="H131" t="s">
         <v>1267</v>
       </c>
-      <c r="I131" s="4" t="s">
-        <v>1311</v>
+      <c r="I131" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J131" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -8273,10 +8292,10 @@
         <v>1267</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>1311</v>
+        <v>1392</v>
       </c>
       <c r="J132" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -8301,8 +8320,11 @@
       <c r="H133" t="s">
         <v>1267</v>
       </c>
-      <c r="I133" s="4" t="s">
-        <v>1311</v>
+      <c r="I133" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1391</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -8315,8 +8337,8 @@
       <c r="C134" t="s">
         <v>1012</v>
       </c>
-      <c r="I134" s="4" t="s">
-        <v>1311</v>
+      <c r="I134" s="1" t="s">
+        <v>1268</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8345,7 +8367,7 @@
         <v>1268</v>
       </c>
       <c r="J135" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8381,11 +8403,11 @@
       <c r="H137" t="s">
         <v>1267</v>
       </c>
-      <c r="I137" s="4" t="s">
-        <v>1311</v>
+      <c r="I137" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J137" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -8432,8 +8454,8 @@
       <c r="H140" t="s">
         <v>1267</v>
       </c>
-      <c r="I140" s="4" t="s">
-        <v>1311</v>
+      <c r="I140" s="1" t="s">
+        <v>1268</v>
       </c>
       <c r="J140" t="s">
         <v>1279</v>
@@ -8465,7 +8487,7 @@
         <v>1268</v>
       </c>
       <c r="J141" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8490,7 +8512,7 @@
         <v>1239</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="E143" t="s">
         <v>1263</v>
@@ -8508,7 +8530,7 @@
         <v>1268</v>
       </c>
       <c r="J143" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8521,9 +8543,12 @@
       <c r="C144" t="s">
         <v>1080</v>
       </c>
+      <c r="I144" s="1" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="A145" s="4" t="s">
         <v>905</v>
       </c>
       <c r="B145" t="s">
@@ -8534,7 +8559,7 @@
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="A146" s="4" t="s">
         <v>906</v>
       </c>
       <c r="B146" s="3" t="s">
@@ -8555,12 +8580,15 @@
       <c r="H146" t="s">
         <v>1267</v>
       </c>
+      <c r="I146" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J146" t="s">
-        <v>1287</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="A147" s="4" t="s">
         <v>907</v>
       </c>
       <c r="B147" t="s">
@@ -8571,7 +8599,7 @@
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="A148" s="4" t="s">
         <v>908</v>
       </c>
       <c r="B148" t="s">
@@ -8582,7 +8610,7 @@
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="A149" s="4" t="s">
         <v>909</v>
       </c>
       <c r="B149" t="s">
@@ -8593,7 +8621,7 @@
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="A150" s="4" t="s">
         <v>910</v>
       </c>
       <c r="B150" s="3" t="s">
@@ -8614,12 +8642,15 @@
       <c r="H150" t="s">
         <v>1267</v>
       </c>
+      <c r="I150" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J150" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="A151" s="4" t="s">
         <v>911</v>
       </c>
       <c r="B151" t="s">
@@ -8630,7 +8661,7 @@
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="4" t="s">
         <v>912</v>
       </c>
       <c r="B152" s="3" t="s">
@@ -8651,12 +8682,15 @@
       <c r="H152" t="s">
         <v>1267</v>
       </c>
+      <c r="I152" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J152" t="s">
-        <v>1288</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="A153" s="4" t="s">
         <v>913</v>
       </c>
       <c r="B153" t="s">
@@ -8667,7 +8701,7 @@
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="A154" s="4" t="s">
         <v>914</v>
       </c>
       <c r="B154" s="3" t="s">
@@ -8688,12 +8722,15 @@
       <c r="H154" t="s">
         <v>1267</v>
       </c>
+      <c r="I154" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J154" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="A155" s="4" t="s">
         <v>915</v>
       </c>
       <c r="B155" s="3" t="s">
@@ -8714,12 +8751,15 @@
       <c r="H155" t="s">
         <v>1267</v>
       </c>
+      <c r="I155" s="1" t="s">
+        <v>1268</v>
+      </c>
       <c r="J155" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="A156" s="4" t="s">
         <v>916</v>
       </c>
       <c r="B156" t="s">
@@ -8730,7 +8770,7 @@
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="A157" s="4" t="s">
         <v>917</v>
       </c>
       <c r="B157" t="s">
@@ -8741,7 +8781,7 @@
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="A158" s="4" t="s">
         <v>918</v>
       </c>
       <c r="B158" t="s">
@@ -8752,7 +8792,7 @@
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="A159" s="4" t="s">
         <v>919</v>
       </c>
       <c r="B159" t="s">
@@ -8763,7 +8803,7 @@
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="A160" s="4" t="s">
         <v>920</v>
       </c>
       <c r="B160" t="s">
@@ -8774,7 +8814,7 @@
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="A161" s="4" t="s">
         <v>921</v>
       </c>
       <c r="B161" t="s">
@@ -8785,7 +8825,7 @@
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="A162" s="4" t="s">
         <v>922</v>
       </c>
       <c r="B162" t="s">
@@ -8796,7 +8836,7 @@
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="A163" s="4" t="s">
         <v>923</v>
       </c>
       <c r="B163" t="s">
@@ -8807,7 +8847,7 @@
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="A164" s="4" t="s">
         <v>924</v>
       </c>
       <c r="B164" t="s">
@@ -8818,7 +8858,7 @@
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="A165" s="4" t="s">
         <v>925</v>
       </c>
       <c r="B165" t="s">
@@ -8829,7 +8869,7 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="A166" s="4" t="s">
         <v>926</v>
       </c>
       <c r="B166" s="3" t="s">
@@ -8850,12 +8890,15 @@
       <c r="H166" t="s">
         <v>1267</v>
       </c>
+      <c r="I166" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J166" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="A167" s="4" t="s">
         <v>1194</v>
       </c>
       <c r="B167" t="s">
@@ -8866,7 +8909,7 @@
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="A168" s="4" t="s">
         <v>1195</v>
       </c>
       <c r="B168" s="3" t="s">
@@ -8887,12 +8930,15 @@
       <c r="H168" t="s">
         <v>1267</v>
       </c>
+      <c r="I168" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J168" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="A169" s="4" t="s">
         <v>1196</v>
       </c>
       <c r="B169" t="s">
@@ -8903,7 +8949,7 @@
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="A170" s="4" t="s">
         <v>1197</v>
       </c>
       <c r="B170" s="3" t="s">
@@ -8927,13 +8973,16 @@
       <c r="H170" t="s">
         <v>1267</v>
       </c>
+      <c r="I170" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J170" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>1315</v>
+      <c r="A171" s="4" t="s">
+        <v>1311</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>1106</v>
@@ -8953,13 +9002,16 @@
       <c r="H171" t="s">
         <v>1267</v>
       </c>
+      <c r="I171" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J171" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>1316</v>
+      <c r="A172" s="4" t="s">
+        <v>1312</v>
       </c>
       <c r="B172" t="s">
         <v>1107</v>
@@ -8969,8 +9021,8 @@
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>1317</v>
+      <c r="A173" s="4" t="s">
+        <v>1313</v>
       </c>
       <c r="B173" t="s">
         <v>1108</v>
@@ -8980,8 +9032,8 @@
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>1318</v>
+      <c r="A174" s="4" t="s">
+        <v>1314</v>
       </c>
       <c r="B174" t="s">
         <v>1109</v>
@@ -8991,8 +9043,8 @@
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>1319</v>
+      <c r="A175" s="4" t="s">
+        <v>1315</v>
       </c>
       <c r="B175" t="s">
         <v>1110</v>
@@ -9002,8 +9054,8 @@
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>1320</v>
+      <c r="A176" s="4" t="s">
+        <v>1316</v>
       </c>
       <c r="B176" t="s">
         <v>1111</v>
@@ -9013,7 +9065,7 @@
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="A177" s="4" t="s">
         <v>1198</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -9034,12 +9086,15 @@
       <c r="H177" t="s">
         <v>1267</v>
       </c>
+      <c r="I177" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J177" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="A178" s="4" t="s">
         <v>1199</v>
       </c>
       <c r="B178" t="s">
@@ -9050,7 +9105,7 @@
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="A179" s="4" t="s">
         <v>1200</v>
       </c>
       <c r="B179" s="3" t="s">
@@ -9071,12 +9126,15 @@
       <c r="H179" t="s">
         <v>1267</v>
       </c>
+      <c r="I179" s="1" t="s">
+        <v>1268</v>
+      </c>
       <c r="J179" t="s">
-        <v>1294</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="A180" s="4" t="s">
         <v>1201</v>
       </c>
       <c r="B180" s="3" t="s">
@@ -9101,14 +9159,14 @@
         <v>1267</v>
       </c>
       <c r="I180" s="4" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="J180" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="A181" s="4" t="s">
         <v>1202</v>
       </c>
       <c r="B181" s="3" t="s">
@@ -9132,12 +9190,15 @@
       <c r="H181" t="s">
         <v>1267</v>
       </c>
+      <c r="I181" s="58" t="s">
+        <v>1268</v>
+      </c>
       <c r="J181" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="A182" s="4" t="s">
         <v>1203</v>
       </c>
       <c r="B182" t="s">
@@ -9148,7 +9209,7 @@
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="A183" s="4" t="s">
         <v>1204</v>
       </c>
       <c r="B183" t="s">
@@ -9159,7 +9220,7 @@
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="A184" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="B184" t="s">
@@ -9170,7 +9231,7 @@
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+      <c r="A185" s="4" t="s">
         <v>1206</v>
       </c>
       <c r="B185" t="s">
@@ -9181,7 +9242,7 @@
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
+      <c r="A186" s="4" t="s">
         <v>1207</v>
       </c>
       <c r="B186" t="s">
@@ -9192,7 +9253,7 @@
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
+      <c r="A187" s="4" t="s">
         <v>1208</v>
       </c>
       <c r="B187" s="3" t="s">
@@ -9213,12 +9274,15 @@
       <c r="H187" t="s">
         <v>1267</v>
       </c>
+      <c r="I187" s="58" t="s">
+        <v>1268</v>
+      </c>
       <c r="J187" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
+      <c r="A188" s="4" t="s">
         <v>1209</v>
       </c>
       <c r="B188" t="s">
@@ -9229,7 +9293,7 @@
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
+      <c r="A189" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="B189" t="s">
@@ -9240,7 +9304,7 @@
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
+      <c r="A190" s="4" t="s">
         <v>1211</v>
       </c>
       <c r="B190" t="s">
@@ -9251,8 +9315,8 @@
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>1321</v>
+      <c r="A191" s="4" t="s">
+        <v>1317</v>
       </c>
       <c r="B191" t="s">
         <v>1126</v>
@@ -9262,8 +9326,8 @@
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>1322</v>
+      <c r="A192" s="4" t="s">
+        <v>1318</v>
       </c>
       <c r="B192" t="s">
         <v>1127</v>
@@ -9273,8 +9337,8 @@
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>1323</v>
+      <c r="A193" s="4" t="s">
+        <v>1319</v>
       </c>
       <c r="B193" t="s">
         <v>1128</v>
@@ -9284,8 +9348,8 @@
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>1325</v>
+      <c r="A194" s="4" t="s">
+        <v>1321</v>
       </c>
       <c r="B194" t="s">
         <v>1129</v>
@@ -9295,8 +9359,8 @@
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>1326</v>
+      <c r="A195" s="4" t="s">
+        <v>1322</v>
       </c>
       <c r="B195" t="s">
         <v>1130</v>
@@ -9306,8 +9370,8 @@
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>1327</v>
+      <c r="A196" s="4" t="s">
+        <v>1323</v>
       </c>
       <c r="B196" t="s">
         <v>1131</v>
@@ -9317,8 +9381,8 @@
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>1328</v>
+      <c r="A197" s="4" t="s">
+        <v>1324</v>
       </c>
       <c r="B197" t="s">
         <v>1132</v>
@@ -9328,8 +9392,8 @@
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>1329</v>
+      <c r="A198" s="4" t="s">
+        <v>1325</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>1133</v>
@@ -9349,13 +9413,16 @@
       <c r="H198" t="s">
         <v>1267</v>
       </c>
+      <c r="I198" s="58" t="s">
+        <v>1268</v>
+      </c>
       <c r="J198" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>1330</v>
+      <c r="A199" s="4" t="s">
+        <v>1326</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>1134</v>
@@ -9375,10 +9442,13 @@
       <c r="H199" t="s">
         <v>1267</v>
       </c>
+      <c r="I199" s="58" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>1331</v>
+      <c r="A200" s="4" t="s">
+        <v>1327</v>
       </c>
       <c r="B200" t="s">
         <v>1135</v>
@@ -9388,8 +9458,8 @@
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>1332</v>
+      <c r="A201" s="4" t="s">
+        <v>1328</v>
       </c>
       <c r="B201" t="s">
         <v>1136</v>
@@ -9399,8 +9469,8 @@
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>1333</v>
+      <c r="A202" s="4" t="s">
+        <v>1329</v>
       </c>
       <c r="B202" t="s">
         <v>1137</v>
@@ -9410,8 +9480,8 @@
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>1334</v>
+      <c r="A203" s="4" t="s">
+        <v>1330</v>
       </c>
       <c r="B203" t="s">
         <v>1138</v>
@@ -9421,8 +9491,8 @@
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>1335</v>
+      <c r="A204" s="4" t="s">
+        <v>1331</v>
       </c>
       <c r="B204" t="s">
         <v>1139</v>
@@ -9432,8 +9502,8 @@
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>1386</v>
+      <c r="A205" s="4" t="s">
+        <v>1382</v>
       </c>
       <c r="B205" t="s">
         <v>1140</v>
@@ -9443,8 +9513,8 @@
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>1336</v>
+      <c r="A206" s="4" t="s">
+        <v>1332</v>
       </c>
       <c r="B206" t="s">
         <v>1141</v>
@@ -9454,8 +9524,8 @@
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>1337</v>
+      <c r="A207" s="4" t="s">
+        <v>1333</v>
       </c>
       <c r="B207" t="s">
         <v>1142</v>
@@ -9465,8 +9535,8 @@
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>1324</v>
+      <c r="A208" s="4" t="s">
+        <v>1320</v>
       </c>
       <c r="B208" t="s">
         <v>1143</v>
@@ -9476,8 +9546,8 @@
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>1338</v>
+      <c r="A209" s="4" t="s">
+        <v>1334</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>1144</v>
@@ -9497,10 +9567,16 @@
       <c r="H209" t="s">
         <v>1267</v>
       </c>
+      <c r="I209" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J209" t="s">
+        <v>1396</v>
+      </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>1339</v>
+      <c r="A210" s="4" t="s">
+        <v>1335</v>
       </c>
       <c r="B210" t="s">
         <v>1145</v>
@@ -9510,8 +9586,8 @@
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>1340</v>
+      <c r="A211" s="4" t="s">
+        <v>1336</v>
       </c>
       <c r="B211" t="s">
         <v>1146</v>
@@ -9521,8 +9597,8 @@
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>1341</v>
+      <c r="A212" s="4" t="s">
+        <v>1337</v>
       </c>
       <c r="B212" t="s">
         <v>1147</v>
@@ -9532,8 +9608,8 @@
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>1342</v>
+      <c r="A213" s="4" t="s">
+        <v>1338</v>
       </c>
       <c r="B213" t="s">
         <v>1148</v>
@@ -9543,8 +9619,8 @@
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>1343</v>
+      <c r="A214" s="4" t="s">
+        <v>1339</v>
       </c>
       <c r="B214" t="s">
         <v>1149</v>
@@ -9554,8 +9630,8 @@
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>1344</v>
+      <c r="A215" s="4" t="s">
+        <v>1340</v>
       </c>
       <c r="B215" t="s">
         <v>1150</v>
@@ -9565,8 +9641,8 @@
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>1345</v>
+      <c r="A216" s="4" t="s">
+        <v>1341</v>
       </c>
       <c r="B216" t="s">
         <v>1151</v>
@@ -9576,8 +9652,8 @@
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>1346</v>
+      <c r="A217" s="4" t="s">
+        <v>1342</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>1152</v>
@@ -9597,13 +9673,16 @@
       <c r="H217" t="s">
         <v>1267</v>
       </c>
+      <c r="I217" s="58" t="s">
+        <v>1268</v>
+      </c>
       <c r="J217" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>1347</v>
+      <c r="A218" s="4" t="s">
+        <v>1343</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>1153</v>
@@ -9623,13 +9702,16 @@
       <c r="H218" t="s">
         <v>1267</v>
       </c>
+      <c r="I218" s="58" t="s">
+        <v>1268</v>
+      </c>
       <c r="J218" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>1348</v>
+      <c r="A219" s="4" t="s">
+        <v>1344</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>1154</v>
@@ -9649,13 +9731,16 @@
       <c r="H219" t="s">
         <v>1267</v>
       </c>
+      <c r="I219" s="4" t="s">
+        <v>1397</v>
+      </c>
       <c r="J219" t="s">
-        <v>533</v>
+        <v>327</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>1349</v>
+      <c r="A220" s="4" t="s">
+        <v>1345</v>
       </c>
       <c r="B220" t="s">
         <v>1155</v>
@@ -9665,8 +9750,8 @@
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>1350</v>
+      <c r="A221" s="4" t="s">
+        <v>1346</v>
       </c>
       <c r="B221" t="s">
         <v>1156</v>
@@ -9676,8 +9761,8 @@
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>1385</v>
+      <c r="A222" s="4" t="s">
+        <v>1381</v>
       </c>
       <c r="B222" t="s">
         <v>1157</v>
@@ -9687,8 +9772,8 @@
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>1351</v>
+      <c r="A223" s="4" t="s">
+        <v>1347</v>
       </c>
       <c r="B223" t="s">
         <v>1158</v>
@@ -9698,8 +9783,8 @@
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>1352</v>
+      <c r="A224" s="4" t="s">
+        <v>1348</v>
       </c>
       <c r="B224" t="s">
         <v>1159</v>
@@ -9709,8 +9794,8 @@
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>1353</v>
+      <c r="A225" s="4" t="s">
+        <v>1349</v>
       </c>
       <c r="B225" t="s">
         <v>1160</v>
@@ -9720,8 +9805,8 @@
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>1354</v>
+      <c r="A226" s="4" t="s">
+        <v>1350</v>
       </c>
       <c r="B226" t="s">
         <v>1161</v>
@@ -9731,8 +9816,8 @@
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>1355</v>
+      <c r="A227" s="4" t="s">
+        <v>1351</v>
       </c>
       <c r="B227" t="s">
         <v>1162</v>
@@ -9742,8 +9827,8 @@
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>1356</v>
+      <c r="A228" s="4" t="s">
+        <v>1352</v>
       </c>
       <c r="B228" t="s">
         <v>1163</v>
@@ -9753,8 +9838,8 @@
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>1357</v>
+      <c r="A229" s="4" t="s">
+        <v>1353</v>
       </c>
       <c r="B229" t="s">
         <v>1164</v>
@@ -9764,8 +9849,8 @@
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>1358</v>
+      <c r="A230" s="4" t="s">
+        <v>1354</v>
       </c>
       <c r="B230" t="s">
         <v>1165</v>
@@ -9775,8 +9860,8 @@
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>1359</v>
+      <c r="A231" s="4" t="s">
+        <v>1355</v>
       </c>
       <c r="B231" t="s">
         <v>1166</v>
@@ -9786,8 +9871,8 @@
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>1360</v>
+      <c r="A232" s="4" t="s">
+        <v>1356</v>
       </c>
       <c r="B232" t="s">
         <v>1167</v>
@@ -9797,8 +9882,8 @@
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>1361</v>
+      <c r="A233" s="4" t="s">
+        <v>1357</v>
       </c>
       <c r="B233" t="s">
         <v>1168</v>
@@ -9808,8 +9893,8 @@
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>1362</v>
+      <c r="A234" s="4" t="s">
+        <v>1358</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>1169</v>
@@ -9829,13 +9914,16 @@
       <c r="H234" t="s">
         <v>1267</v>
       </c>
+      <c r="I234" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J234" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>1363</v>
+      <c r="A235" s="4" t="s">
+        <v>1359</v>
       </c>
       <c r="B235" t="s">
         <v>1170</v>
@@ -9845,8 +9933,8 @@
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>1364</v>
+      <c r="A236" s="4" t="s">
+        <v>1360</v>
       </c>
       <c r="B236" t="s">
         <v>1171</v>
@@ -9856,8 +9944,8 @@
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>1365</v>
+      <c r="A237" s="4" t="s">
+        <v>1361</v>
       </c>
       <c r="B237" t="s">
         <v>1172</v>
@@ -9867,8 +9955,8 @@
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>1366</v>
+      <c r="A238" s="4" t="s">
+        <v>1362</v>
       </c>
       <c r="B238" t="s">
         <v>1173</v>
@@ -9878,8 +9966,8 @@
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>1384</v>
+      <c r="A239" s="4" t="s">
+        <v>1380</v>
       </c>
       <c r="B239" t="s">
         <v>1174</v>
@@ -9889,8 +9977,8 @@
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>1367</v>
+      <c r="A240" s="4" t="s">
+        <v>1363</v>
       </c>
       <c r="B240" t="s">
         <v>1175</v>
@@ -9900,8 +9988,8 @@
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>1368</v>
+      <c r="A241" s="4" t="s">
+        <v>1364</v>
       </c>
       <c r="B241" t="s">
         <v>1176</v>
@@ -9911,8 +9999,8 @@
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>1369</v>
+      <c r="A242" s="4" t="s">
+        <v>1365</v>
       </c>
       <c r="B242" t="s">
         <v>1177</v>
@@ -9922,8 +10010,8 @@
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>1370</v>
+      <c r="A243" s="4" t="s">
+        <v>1366</v>
       </c>
       <c r="B243" t="s">
         <v>1178</v>
@@ -9933,8 +10021,8 @@
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>1371</v>
+      <c r="A244" s="4" t="s">
+        <v>1367</v>
       </c>
       <c r="B244" t="s">
         <v>1179</v>
@@ -9944,8 +10032,8 @@
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>1372</v>
+      <c r="A245" s="4" t="s">
+        <v>1368</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>1193</v>
@@ -9966,15 +10054,15 @@
         <v>1267</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="J245" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>1373</v>
+      <c r="A246" s="4" t="s">
+        <v>1369</v>
       </c>
       <c r="B246" t="s">
         <v>1181</v>
@@ -9984,8 +10072,8 @@
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>1374</v>
+      <c r="A247" s="4" t="s">
+        <v>1370</v>
       </c>
       <c r="B247" t="s">
         <v>1182</v>
@@ -9995,8 +10083,8 @@
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>1375</v>
+      <c r="A248" s="4" t="s">
+        <v>1371</v>
       </c>
       <c r="B248" t="s">
         <v>1183</v>
@@ -10006,8 +10094,8 @@
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>1376</v>
+      <c r="A249" s="4" t="s">
+        <v>1372</v>
       </c>
       <c r="B249" t="s">
         <v>1184</v>
@@ -10017,8 +10105,8 @@
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>1377</v>
+      <c r="A250" s="4" t="s">
+        <v>1373</v>
       </c>
       <c r="B250" s="55" t="s">
         <v>1185</v>
@@ -10033,8 +10121,8 @@
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>1378</v>
+      <c r="A251" s="4" t="s">
+        <v>1374</v>
       </c>
       <c r="B251" t="s">
         <v>1186</v>
@@ -10044,8 +10132,8 @@
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>1379</v>
+      <c r="A252" s="4" t="s">
+        <v>1375</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>1187</v>
@@ -10065,13 +10153,16 @@
       <c r="H252" t="s">
         <v>1267</v>
       </c>
+      <c r="I252" s="4" t="s">
+        <v>1306</v>
+      </c>
       <c r="J252" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="C253" s="54" t="s">
         <v>1189</v>
@@ -10089,12 +10180,12 @@
         <v>1267</v>
       </c>
       <c r="J253" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="C254" s="54" t="s">
         <v>1190</v>
@@ -10112,12 +10203,12 @@
         <v>1267</v>
       </c>
       <c r="J254" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="C255" s="54" t="s">
         <v>1188</v>
@@ -10135,12 +10226,12 @@
         <v>1267</v>
       </c>
       <c r="J255" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C256" t="s">
         <v>1092</v>
@@ -23901,8 +23992,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C8:C14">
-    <cfRule type="duplicateValues" dxfId="137" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:C18">
     <cfRule type="duplicateValues" dxfId="135" priority="92"/>
@@ -23921,8 +24012,8 @@
     <cfRule type="duplicateValues" dxfId="130" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C47">
-    <cfRule type="duplicateValues" dxfId="129" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48:C53">
     <cfRule type="duplicateValues" dxfId="127" priority="80"/>
@@ -23934,8 +24025,8 @@
     <cfRule type="duplicateValues" dxfId="125" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C62">
-    <cfRule type="duplicateValues" dxfId="124" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C63:C70">
     <cfRule type="duplicateValues" dxfId="122" priority="94"/>
@@ -23974,8 +24065,8 @@
     <cfRule type="duplicateValues" dxfId="111" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18:L21">
-    <cfRule type="duplicateValues" dxfId="110" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
     <cfRule type="duplicateValues" dxfId="108" priority="515"/>
@@ -23987,8 +24078,8 @@
     <cfRule type="duplicateValues" dxfId="106" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44:L48">
-    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L50:L51">
     <cfRule type="duplicateValues" dxfId="103" priority="105"/>
@@ -24082,12 +24173,12 @@
     <cfRule type="duplicateValues" dxfId="73" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U13">
-    <cfRule type="duplicateValues" dxfId="72" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U14:U15">
-    <cfRule type="duplicateValues" dxfId="70" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U16">
     <cfRule type="duplicateValues" dxfId="68" priority="61"/>
@@ -24111,16 +24202,16 @@
     <cfRule type="duplicateValues" dxfId="62" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U29">
-    <cfRule type="duplicateValues" dxfId="61" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U30">
-    <cfRule type="duplicateValues" dxfId="59" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="duplicateValues" dxfId="57" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
     <cfRule type="duplicateValues" dxfId="55" priority="47"/>
@@ -24143,8 +24234,8 @@
     <cfRule type="duplicateValues" dxfId="48" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U43:U45">
-    <cfRule type="duplicateValues" dxfId="47" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
     <cfRule type="duplicateValues" dxfId="45" priority="39"/>

--- a/Notes/datamapping-MOVES.xlsx
+++ b/Notes/datamapping-MOVES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318E2B62-4B8F-42A0-984C-60D7B6DA38FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0160A33-6455-4F91-B8D7-CBC38E3A5BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1982F562-5184-46C6-89BD-68E4E108BC42}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{1982F562-5184-46C6-89BD-68E4E108BC42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4767" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4768" uniqueCount="1398">
   <si>
     <t>bug</t>
   </si>
@@ -1863,9 +1863,6 @@
     <t>?can add paralyze to EFFECT_FLY?</t>
   </si>
   <si>
-    <t>EFFECT_ALL_UP_HIT</t>
-  </si>
-  <si>
     <t>EFFECT_MULTI_HIT</t>
   </si>
   <si>
@@ -3816,9 +3813,6 @@
     <t>const DISCHARGE</t>
   </si>
   <si>
-    <t>const OMINOUS_WIND</t>
-  </si>
-  <si>
     <t>const ZEN_HEADBUTT</t>
   </si>
   <si>
@@ -4233,7 +4227,13 @@
     <t>ACID, ground</t>
   </si>
   <si>
-    <t>hex</t>
+    <t>const HEX</t>
+  </si>
+  <si>
+    <t>cond+</t>
+  </si>
+  <si>
+    <t>EFFECT_HEX</t>
   </si>
 </sst>
 </file>
@@ -6317,1107 +6317,1107 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H5" t="s">
         <v>1265</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>1267</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E6" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H6" t="s">
         <v>1265</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H6" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J6" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B9" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C9" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C11" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E12" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H12" t="s">
         <v>1265</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H12" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" t="s">
         <v>1268</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B13" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C13" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E14" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H14" t="s">
         <v>1265</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H14" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J14" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E16" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H16" t="s">
         <v>1265</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H16" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J16" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B17" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C17" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B18" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C18" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E19" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H19" t="s">
         <v>1265</v>
       </c>
-      <c r="G19" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H19" t="s">
-        <v>1267</v>
-      </c>
       <c r="J19" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E20" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H20" t="s">
         <v>1265</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H20" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J20" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E21" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H21" t="s">
         <v>1265</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H21" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J21" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E22" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H22" t="s">
         <v>1265</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H22" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J22" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B23" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C23" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B24" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C24" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B25" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C25" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E26" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H26" t="s">
         <v>1265</v>
       </c>
-      <c r="G26" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H26" t="s">
-        <v>1267</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="J26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B27" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C27" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E28" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H28" t="s">
         <v>1265</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H28" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J28" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E29" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H29" t="s">
         <v>1265</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H29" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J29" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B30" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C30" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B31" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C31" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E32" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H32" t="s">
         <v>1265</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H32" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J32" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B33" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C33" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E34" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H34" t="s">
         <v>1265</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H34" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J34" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C35" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G35" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B36" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C36" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G36" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B37" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C37" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B38" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C38" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B39" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C39" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E40" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H40" t="s">
         <v>1265</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H40" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J40" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B41" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C41" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C42" s="52" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E42" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H42" t="s">
         <v>1265</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H42" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J42" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B43" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C43" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B44" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C44" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B45" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C45" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B46" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C46" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B47" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C47" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B48" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C48" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B49" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C49" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C50" s="54" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E50" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H50" t="s">
         <v>1265</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H50" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J50" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B52" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C52" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B53" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C53" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B54" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C54" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E55" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H55" t="s">
         <v>1265</v>
       </c>
-      <c r="G55" t="s">
+      <c r="I55" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H55" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J55" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B56" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C56" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B57" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C57" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B58" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C58" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B59" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C59" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B60" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C60" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B61" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C61" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B62" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C62" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B63" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C63" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B64" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C64" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B65" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C65" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B66" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C66" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B67" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C67" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E68" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H68" t="s">
         <v>1265</v>
       </c>
-      <c r="G68" t="s">
+      <c r="I68" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="H68" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="J68" t="s">
         <v>58</v>
@@ -7425,50 +7425,50 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B69" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C69" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B70" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C70" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C71" s="52" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E71" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H71" t="s">
         <v>1265</v>
       </c>
-      <c r="G71" t="s">
+      <c r="I71" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="H71" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="J71" t="s">
         <v>42</v>
@@ -7476,306 +7476,306 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B72" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C72" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B73" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C73" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B74" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C74" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B75" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C75" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B76" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C76" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B77" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C77" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B78" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C78" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B79" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C79" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B80" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C80" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B81" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C81" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B82" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C82" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B83" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C83" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B84" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C84" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B85" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C85" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B86" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C86" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B87" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C87" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B88" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C88" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B89" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C89" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B90" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C90" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B91" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C91" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B92" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C92" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B93" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C93" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B94" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C94" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B95" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C95" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B96" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C96" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C97" s="54" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E97" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="G97" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H97" t="s">
         <v>1265</v>
       </c>
-      <c r="G97" t="s">
+      <c r="I97" s="1" t="s">
         <v>1266</v>
-      </c>
-      <c r="H97" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>1268</v>
       </c>
       <c r="J97" t="s">
         <v>89</v>
@@ -7783,867 +7783,867 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B98" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C98" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B99" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C99" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B100" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C100" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B101" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C101" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B102" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C102" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C103" s="52" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E103" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="G103" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H103" t="s">
         <v>1265</v>
       </c>
-      <c r="G103" t="s">
+      <c r="I103" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H103" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J103" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B104" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C104" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B105" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C105" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B106" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C106" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B107" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C107" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B108" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C108" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B109" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C109" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B110" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C110" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C111" s="52" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E111" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="G111" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H111" t="s">
         <v>1265</v>
       </c>
-      <c r="G111" t="s">
+      <c r="I111" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H111" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J111" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B112" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C112" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G112" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B113" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C113" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G113" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B114" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C114" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B115" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C115" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B116" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C116" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B117" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C117" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B118" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C118" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B119" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C119" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E120" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="G120" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H120" t="s">
         <v>1265</v>
       </c>
-      <c r="G120" t="s">
+      <c r="I120" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H120" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J120" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B121" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C121" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E122" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="G122" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H122" t="s">
         <v>1265</v>
       </c>
-      <c r="G122" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H122" t="s">
-        <v>1267</v>
-      </c>
       <c r="I122" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J122" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B123" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C123" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B124" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C124" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B125" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C125" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B126" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C126" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B127" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C127" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B128" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C128" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C129" s="52" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E129" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="G129" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H129" t="s">
         <v>1265</v>
       </c>
-      <c r="G129" t="s">
+      <c r="I129" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H129" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J129" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B130" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C130" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C131" s="52" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E131" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="G131" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H131" t="s">
         <v>1265</v>
       </c>
-      <c r="G131" t="s">
+      <c r="I131" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H131" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J131" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C132" s="54" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E132" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="G132" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H132" t="s">
         <v>1265</v>
       </c>
-      <c r="G132" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H132" t="s">
-        <v>1267</v>
-      </c>
       <c r="I132" s="4" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="J132" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C133" s="52" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E133" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="G133" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H133" t="s">
         <v>1265</v>
       </c>
-      <c r="G133" t="s">
+      <c r="I133" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H133" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J133" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B134" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C134" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C135" s="52" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E135" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="G135" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H135" t="s">
         <v>1265</v>
       </c>
-      <c r="G135" t="s">
+      <c r="I135" s="57" t="s">
         <v>1266</v>
       </c>
-      <c r="H135" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I135" s="57" t="s">
-        <v>1268</v>
-      </c>
       <c r="J135" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B136" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C136" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C137" s="52" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E137" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="G137" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H137" t="s">
         <v>1265</v>
       </c>
-      <c r="G137" t="s">
+      <c r="I137" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H137" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I137" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J137" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B138" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C138" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B139" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C139" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C140" s="52" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E140" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="G140" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H140" t="s">
         <v>1265</v>
       </c>
-      <c r="G140" t="s">
+      <c r="I140" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H140" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J140" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C141" s="52" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E141" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="G141" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H141" t="s">
         <v>1265</v>
       </c>
-      <c r="G141" t="s">
+      <c r="I141" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H141" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J141" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B142" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C142" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C143" s="52" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="E143" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="G143" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H143" t="s">
         <v>1265</v>
       </c>
-      <c r="G143" t="s">
+      <c r="I143" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H143" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J143" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B144" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C144" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B145" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C145" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C146" s="52" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E146" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="G146" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H146" t="s">
         <v>1265</v>
       </c>
-      <c r="G146" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H146" t="s">
-        <v>1267</v>
-      </c>
       <c r="I146" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J146" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B147" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C147" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B148" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C148" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B149" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C149" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C150" s="52" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E150" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F150" s="1" t="s">
+      <c r="G150" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H150" t="s">
         <v>1265</v>
       </c>
-      <c r="G150" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H150" t="s">
-        <v>1267</v>
-      </c>
       <c r="I150" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J150" t="s">
         <v>146</v>
@@ -8651,515 +8651,515 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B151" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C151" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C152" s="52" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E152" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="G152" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H152" t="s">
         <v>1265</v>
       </c>
-      <c r="G152" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H152" t="s">
-        <v>1267</v>
-      </c>
       <c r="I152" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J152" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B153" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C153" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C154" s="52" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E154" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="G154" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H154" t="s">
         <v>1265</v>
       </c>
-      <c r="G154" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H154" t="s">
-        <v>1267</v>
-      </c>
       <c r="I154" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J154" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C155" s="52" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E155" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="G155" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H155" t="s">
         <v>1265</v>
       </c>
-      <c r="G155" t="s">
+      <c r="I155" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H155" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J155" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B156" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C156" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B157" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C157" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B158" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C158" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B159" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C159" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B160" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C160" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B161" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C161" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B162" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C162" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B163" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C163" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B164" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C164" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B165" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C165" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C166" s="54" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E166" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F166" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F166" s="1" t="s">
+      <c r="G166" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H166" t="s">
         <v>1265</v>
       </c>
-      <c r="G166" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H166" t="s">
-        <v>1267</v>
-      </c>
       <c r="I166" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J166" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B167" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C167" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C168" s="52" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E168" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F168" s="1" t="s">
+      <c r="G168" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H168" t="s">
         <v>1265</v>
       </c>
-      <c r="G168" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H168" t="s">
-        <v>1267</v>
-      </c>
       <c r="I168" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J168" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B169" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C169" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C170" s="52" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E170" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F170" s="1" t="s">
+      <c r="G170" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H170" t="s">
         <v>1265</v>
       </c>
-      <c r="G170" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H170" t="s">
-        <v>1267</v>
-      </c>
       <c r="I170" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J170" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C171" s="52" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E171" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F171" s="1" t="s">
+      <c r="G171" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H171" t="s">
         <v>1265</v>
       </c>
-      <c r="G171" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H171" t="s">
-        <v>1267</v>
-      </c>
       <c r="I171" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J171" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B172" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C172" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B173" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C173" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B174" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C174" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B175" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C175" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B176" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C176" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C177" s="52" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E177" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F177" s="1" t="s">
+      <c r="G177" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H177" t="s">
         <v>1265</v>
       </c>
-      <c r="G177" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H177" t="s">
-        <v>1267</v>
-      </c>
       <c r="I177" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J177" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B178" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C178" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C179" s="52" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E179" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F179" s="1" t="s">
+      <c r="G179" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H179" t="s">
         <v>1265</v>
       </c>
-      <c r="G179" t="s">
+      <c r="I179" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="H179" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I179" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="J179" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C180" s="52" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E180" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F180" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F180" s="1" t="s">
+      <c r="G180" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H180" t="s">
         <v>1265</v>
       </c>
-      <c r="G180" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H180" t="s">
-        <v>1267</v>
-      </c>
       <c r="I180" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J180" t="s">
         <v>61</v>
@@ -9167,572 +9167,572 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C181" s="52" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E181" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F181" s="1" t="s">
+      <c r="G181" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H181" t="s">
         <v>1265</v>
       </c>
-      <c r="G181" t="s">
+      <c r="I181" s="58" t="s">
         <v>1266</v>
       </c>
-      <c r="H181" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I181" s="58" t="s">
-        <v>1268</v>
-      </c>
       <c r="J181" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B182" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C182" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B183" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C183" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B184" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C184" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B185" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C185" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B186" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C186" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C187" s="52" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E187" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F187" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="G187" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H187" t="s">
         <v>1265</v>
       </c>
-      <c r="G187" t="s">
+      <c r="I187" s="58" t="s">
         <v>1266</v>
       </c>
-      <c r="H187" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I187" s="58" t="s">
-        <v>1268</v>
-      </c>
       <c r="J187" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B188" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C188" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B189" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C189" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B190" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C190" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B191" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C191" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="B192" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C192" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B193" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C193" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B194" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C194" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B195" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C195" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B196" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C196" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B197" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C197" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C198" s="52" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E198" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F198" s="1" t="s">
+      <c r="G198" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H198" t="s">
         <v>1265</v>
       </c>
-      <c r="G198" t="s">
+      <c r="I198" s="58" t="s">
         <v>1266</v>
       </c>
-      <c r="H198" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I198" s="58" t="s">
-        <v>1268</v>
-      </c>
       <c r="J198" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C199" s="52" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E199" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F199" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="G199" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H199" t="s">
         <v>1265</v>
       </c>
-      <c r="G199" t="s">
+      <c r="I199" s="58" t="s">
         <v>1266</v>
-      </c>
-      <c r="H199" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I199" s="58" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B200" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C200" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B201" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C201" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B202" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C202" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B203" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C203" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="B204" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C204" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B205" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C205" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B206" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C206" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B207" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C207" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B208" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C208" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C209" s="52" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E209" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F209" s="1" t="s">
+      <c r="G209" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H209" t="s">
         <v>1265</v>
       </c>
-      <c r="G209" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H209" t="s">
-        <v>1267</v>
-      </c>
       <c r="I209" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J209" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B210" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C210" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B211" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C211" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="B212" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C212" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B213" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C213" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B214" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C214" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B215" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C215" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B216" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C216" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C217" s="52" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E217" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F217" s="1" t="s">
+      <c r="G217" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H217" t="s">
         <v>1265</v>
       </c>
-      <c r="G217" t="s">
+      <c r="I217" s="58" t="s">
         <v>1266</v>
       </c>
-      <c r="H217" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I217" s="58" t="s">
-        <v>1268</v>
-      </c>
       <c r="J217" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C218" s="52" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E218" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F218" s="1" t="s">
+      <c r="G218" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H218" t="s">
         <v>1265</v>
       </c>
-      <c r="G218" t="s">
+      <c r="I218" s="58" t="s">
         <v>1266</v>
       </c>
-      <c r="H218" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I218" s="58" t="s">
-        <v>1268</v>
-      </c>
       <c r="J218" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C219" s="52" t="s">
-        <v>1258</v>
+        <v>1395</v>
       </c>
       <c r="E219" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F219" s="1" t="s">
+      <c r="G219" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H219" t="s">
         <v>1265</v>
       </c>
-      <c r="G219" t="s">
+      <c r="I219" s="58" t="s">
         <v>1266</v>
-      </c>
-      <c r="H219" t="s">
-        <v>1267</v>
-      </c>
-      <c r="I219" s="4" t="s">
-        <v>1397</v>
       </c>
       <c r="J219" t="s">
         <v>327</v>
@@ -9740,321 +9740,321 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B220" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C220" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="B221" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C221" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="B222" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C222" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B223" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C223" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="B224" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C224" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B225" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C225" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="B226" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C226" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B227" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C227" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="B228" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C228" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B229" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C229" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="B230" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C230" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B231" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C231" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B232" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C232" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B233" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C233" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="E234" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F234" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F234" s="1" t="s">
+      <c r="G234" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H234" t="s">
         <v>1265</v>
       </c>
-      <c r="G234" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H234" t="s">
-        <v>1267</v>
-      </c>
       <c r="I234" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J234" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B235" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C235" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B236" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C236" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B237" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C237" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B238" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C238" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B239" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C239" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B240" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C240" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B241" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C241" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="B242" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C242" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B243" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C243" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="B244" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C244" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C245" s="54" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E245" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F245" s="1" t="s">
+      <c r="G245" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H245" t="s">
         <v>1265</v>
       </c>
-      <c r="G245" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H245" t="s">
-        <v>1267</v>
-      </c>
       <c r="I245" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J245" t="s">
         <v>89</v>
@@ -10062,57 +10062,57 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="B246" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C246" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B247" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C247" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="B248" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C248" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B249" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C249" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="B250" s="55" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C250" s="56" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="D250" s="55"/>
       <c r="E250" s="5"/>
@@ -10122,122 +10122,122 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B251" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C251" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C252" s="52" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E252" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F252" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F252" s="1" t="s">
+      <c r="G252" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H252" t="s">
         <v>1265</v>
       </c>
-      <c r="G252" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H252" t="s">
-        <v>1267</v>
-      </c>
       <c r="I252" s="4" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="J252" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="C253" s="54" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E253" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F253" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F253" s="1" t="s">
+      <c r="G253" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H253" t="s">
         <v>1265</v>
       </c>
-      <c r="G253" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H253" t="s">
-        <v>1267</v>
-      </c>
       <c r="J253" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="C254" s="54" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E254" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F254" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F254" s="1" t="s">
+      <c r="G254" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H254" t="s">
         <v>1265</v>
       </c>
-      <c r="G254" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H254" t="s">
-        <v>1267</v>
-      </c>
       <c r="J254" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="C255" s="54" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E255" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F255" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="F255" s="1" t="s">
+      <c r="G255" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H255" t="s">
         <v>1265</v>
       </c>
-      <c r="G255" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H255" t="s">
-        <v>1267</v>
-      </c>
       <c r="J255" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="C256" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G256" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -10425,7 +10425,7 @@
         <v>167</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="J5" t="s">
         <v>269</v>
@@ -10466,7 +10466,7 @@
         <v>236</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J6" t="s">
         <v>270</v>
@@ -10691,13 +10691,13 @@
         <v>167</v>
       </c>
       <c r="H12" s="40" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J12" t="s">
         <v>298</v>
       </c>
       <c r="K12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -10779,7 +10779,7 @@
         <v>586</v>
       </c>
       <c r="H14" s="42" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I14" s="39" t="s">
         <v>352</v>
@@ -10861,7 +10861,7 @@
         <v>576</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I16" s="39" t="s">
         <v>576</v>
@@ -10943,7 +10943,7 @@
         <v>20</v>
       </c>
       <c r="L18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -11071,7 +11071,7 @@
         <v>292</v>
       </c>
       <c r="H21" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J21" t="s">
         <v>276</v>
@@ -11115,7 +11115,7 @@
         <v>124</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J22" t="s">
         <v>277</v>
@@ -11270,7 +11270,7 @@
         <v>355</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I26" s="39" t="s">
         <v>355</v>
@@ -11352,13 +11352,13 @@
         <v>58</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J28" t="s">
         <v>302</v>
       </c>
       <c r="K28" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -11393,7 +11393,7 @@
         <v>202</v>
       </c>
       <c r="H29" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J29" t="s">
         <v>303</v>
@@ -11504,7 +11504,7 @@
         <v>167</v>
       </c>
       <c r="H32" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J32" t="s">
         <v>304</v>
@@ -11557,7 +11557,7 @@
         <v>272</v>
       </c>
       <c r="K33" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="M33">
         <v>3</v>
@@ -11589,7 +11589,7 @@
         <v>37</v>
       </c>
       <c r="H34" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J34" t="s">
         <v>273</v>
@@ -11820,7 +11820,7 @@
         <v>128</v>
       </c>
       <c r="H40" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J40" t="s">
         <v>278</v>
@@ -11896,7 +11896,7 @@
         <v>483</v>
       </c>
       <c r="H42" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J42" t="s">
         <v>279</v>
@@ -11993,7 +11993,7 @@
         <v>20</v>
       </c>
       <c r="S44" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -12171,13 +12171,13 @@
         <v>280</v>
       </c>
       <c r="H50" s="40" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="J50" t="s">
         <v>280</v>
       </c>
       <c r="K50" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M50">
         <v>2</v>
@@ -12325,7 +12325,7 @@
         <v>10</v>
       </c>
       <c r="H55" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J55" t="s">
         <v>281</v>
@@ -12819,13 +12819,13 @@
         <v>58</v>
       </c>
       <c r="H68" s="40" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J68" t="s">
         <v>58</v>
       </c>
       <c r="K68" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M68">
         <v>4</v>
@@ -12942,7 +12942,7 @@
         <v>576</v>
       </c>
       <c r="H71" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I71" s="39" t="s">
         <v>576</v>
@@ -13879,7 +13879,7 @@
         <v>51</v>
       </c>
       <c r="H97" s="40" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="J97" t="s">
         <v>283</v>
@@ -14073,7 +14073,7 @@
         <v>586</v>
       </c>
       <c r="H103" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I103" s="39" t="s">
         <v>382</v>
@@ -14187,7 +14187,7 @@
         <v>154</v>
       </c>
       <c r="H111" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J111" t="s">
         <v>309</v>
@@ -14316,7 +14316,7 @@
         <v>431</v>
       </c>
       <c r="H120" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J120" t="s">
         <v>286</v>
@@ -14362,7 +14362,7 @@
         <v>586</v>
       </c>
       <c r="H122" s="40" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I122" s="39" t="s">
         <v>388</v>
@@ -14466,7 +14466,7 @@
         <v>434</v>
       </c>
       <c r="H129" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J129" t="s">
         <v>289</v>
@@ -14512,7 +14512,7 @@
         <v>586</v>
       </c>
       <c r="H131" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I131" s="39" t="s">
         <v>391</v>
@@ -14535,7 +14535,7 @@
         <v>98</v>
       </c>
       <c r="H132" s="40" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J132" t="s">
         <v>291</v>
@@ -14552,7 +14552,7 @@
         <v>292</v>
       </c>
       <c r="H133" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J133" t="s">
         <v>292</v>
@@ -14586,7 +14586,7 @@
         <v>347</v>
       </c>
       <c r="H135" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J135" t="s">
         <v>293</v>
@@ -14609,7 +14609,7 @@
         <v>438</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>392</v>
@@ -14618,7 +14618,7 @@
         <v>294</v>
       </c>
       <c r="L136" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -14629,7 +14629,7 @@
         <v>103</v>
       </c>
       <c r="H137" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J137" t="s">
         <v>103</v>
@@ -14680,7 +14680,7 @@
         <v>310</v>
       </c>
       <c r="H140" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J140" t="s">
         <v>313</v>
@@ -14700,7 +14700,7 @@
         <v>37</v>
       </c>
       <c r="H141" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J141" t="s">
         <v>314</v>
@@ -14737,7 +14737,7 @@
         <v>439</v>
       </c>
       <c r="H143" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J143" t="s">
         <v>315</v>
@@ -14794,7 +14794,7 @@
         <v>52</v>
       </c>
       <c r="H146" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J146" t="s">
         <v>295</v>
@@ -14856,7 +14856,7 @@
         <v>586</v>
       </c>
       <c r="H150" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I150" s="39" t="s">
         <v>397</v>
@@ -14890,7 +14890,7 @@
         <v>85</v>
       </c>
       <c r="H152" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J152" t="s">
         <v>297</v>
@@ -14907,13 +14907,13 @@
         <v>113</v>
       </c>
       <c r="H153" s="53" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J153" t="s">
         <v>113</v>
       </c>
       <c r="L153" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -14930,7 +14930,7 @@
         <v>586</v>
       </c>
       <c r="H154" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I154" s="39" t="s">
         <v>398</v>
@@ -14953,7 +14953,7 @@
         <v>167</v>
       </c>
       <c r="H155" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J155" t="s">
         <v>317</v>
@@ -15046,7 +15046,7 @@
         <v>173</v>
       </c>
       <c r="L161" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -15116,7 +15116,7 @@
         <v>469</v>
       </c>
       <c r="H166" s="40" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J166" t="s">
         <v>268</v>
@@ -15150,7 +15150,7 @@
         <v>350</v>
       </c>
       <c r="H168" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J168" t="s">
         <v>319</v>
@@ -15187,7 +15187,7 @@
         <v>225</v>
       </c>
       <c r="H170" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J170" t="s">
         <v>320</v>
@@ -15210,7 +15210,7 @@
         <v>206</v>
       </c>
       <c r="H171" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J171" t="s">
         <v>321</v>
@@ -15233,7 +15233,7 @@
         <v>442</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>427</v>
@@ -15245,7 +15245,7 @@
         <v>7</v>
       </c>
       <c r="L172" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -15279,7 +15279,7 @@
         <v>227</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>412</v>
@@ -15288,7 +15288,7 @@
         <v>324</v>
       </c>
       <c r="L174" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -15333,7 +15333,7 @@
         <v>441</v>
       </c>
       <c r="H177" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J177" t="s">
         <v>349</v>
@@ -15364,7 +15364,7 @@
         <v>443</v>
       </c>
       <c r="H179" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J179" t="s">
         <v>326</v>
@@ -15373,7 +15373,7 @@
         <v>591</v>
       </c>
       <c r="L179" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -15384,7 +15384,7 @@
         <v>192</v>
       </c>
       <c r="H180" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J180" t="s">
         <v>192</v>
@@ -15404,7 +15404,7 @@
         <v>47</v>
       </c>
       <c r="H181" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J181" t="s">
         <v>327</v>
@@ -15485,13 +15485,13 @@
         <v>199</v>
       </c>
       <c r="H187" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J187" t="s">
         <v>199</v>
       </c>
       <c r="K187" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -15633,7 +15633,7 @@
         <v>195</v>
       </c>
       <c r="H198" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J198" t="s">
         <v>329</v>
@@ -15653,7 +15653,7 @@
         <v>436</v>
       </c>
       <c r="H199" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J199" t="s">
         <v>330</v>
@@ -15811,7 +15811,7 @@
         <v>444</v>
       </c>
       <c r="H209" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J209" t="s">
         <v>332</v>
@@ -15820,7 +15820,7 @@
         <v>84</v>
       </c>
       <c r="L209" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -15863,7 +15863,7 @@
         <v>333</v>
       </c>
       <c r="L211" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -15922,7 +15922,7 @@
         <v>227</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I215" s="3" t="s">
         <v>420</v>
@@ -15931,7 +15931,7 @@
         <v>227</v>
       </c>
       <c r="L215" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -15959,7 +15959,7 @@
         <v>229</v>
       </c>
       <c r="H217" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J217" t="s">
         <v>229</v>
@@ -15979,7 +15979,7 @@
         <v>445</v>
       </c>
       <c r="H218" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J218" t="s">
         <v>334</v>
@@ -15999,7 +15999,7 @@
         <v>446</v>
       </c>
       <c r="H219" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J219" t="s">
         <v>335</v>
@@ -16155,7 +16155,7 @@
         <v>448</v>
       </c>
       <c r="G231" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I231" s="3" t="s">
         <v>411</v>
@@ -16164,7 +16164,7 @@
         <v>336</v>
       </c>
       <c r="L231" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -16206,13 +16206,13 @@
         <v>449</v>
       </c>
       <c r="H234" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J234" t="s">
         <v>337</v>
       </c>
       <c r="K234" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
@@ -16375,7 +16375,7 @@
         <v>451</v>
       </c>
       <c r="H245" s="40" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J245" t="s">
         <v>342</v>
@@ -16457,7 +16457,7 @@
         <v>262</v>
       </c>
       <c r="L250" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
@@ -16485,7 +16485,7 @@
         <v>1</v>
       </c>
       <c r="H252" s="41" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J252" t="s">
         <v>343</v>
@@ -16502,7 +16502,7 @@
         <v>78</v>
       </c>
       <c r="H253" s="40" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J253">
         <v>252</v>
@@ -16516,7 +16516,7 @@
         <v>266</v>
       </c>
       <c r="H254" s="40" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J254">
         <v>253</v>
@@ -16530,7 +16530,7 @@
         <v>267</v>
       </c>
       <c r="H255" s="40" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J255">
         <v>254</v>
@@ -16544,7 +16544,7 @@
         <v>268</v>
       </c>
       <c r="J256" s="38" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="257" spans="4:10" x14ac:dyDescent="0.25">
@@ -17298,7 +17298,7 @@
         <v>598</v>
       </c>
       <c r="AG4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -18113,7 +18113,7 @@
         <v>572</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -18321,7 +18321,7 @@
         <v>4</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="V19" s="10">
         <v>60</v>
@@ -18333,7 +18333,7 @@
         <v>10</v>
       </c>
       <c r="Y19" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Z19" s="8" t="s">
         <v>572</v>
@@ -18342,7 +18342,7 @@
         <v>572</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -18401,7 +18401,7 @@
         <v>4</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="V20" s="10">
         <v>60</v>
@@ -18413,7 +18413,7 @@
         <v>20</v>
       </c>
       <c r="Y20" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Z20" s="8">
         <v>100</v>
@@ -18422,10 +18422,10 @@
         <v>572</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AG20" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -18828,7 +18828,7 @@
         <v>572</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="AG26" s="4" t="s">
         <v>606</v>
@@ -19169,28 +19169,28 @@
         <v>7</v>
       </c>
       <c r="U31" s="6" t="s">
-        <v>528</v>
+        <v>36</v>
       </c>
       <c r="V31" s="10">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="W31" s="9">
         <v>1</v>
       </c>
       <c r="X31" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="s">
-        <v>521</v>
-      </c>
-      <c r="Z31" s="8">
-        <v>10</v>
+        <v>1396</v>
+      </c>
+      <c r="Z31" s="8" t="s">
+        <v>572</v>
       </c>
       <c r="AA31" s="36" t="s">
         <v>572</v>
       </c>
-      <c r="AE31" t="s">
-        <v>607</v>
+      <c r="AE31" s="4" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
@@ -19327,7 +19327,7 @@
         <v>12</v>
       </c>
       <c r="AE33" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
@@ -19840,7 +19840,7 @@
         <v>572</v>
       </c>
       <c r="AE40" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
@@ -19920,7 +19920,7 @@
         <v>572</v>
       </c>
       <c r="AE41" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
@@ -20106,7 +20106,7 @@
         <v>572</v>
       </c>
       <c r="AE44" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.25">
@@ -20186,7 +20186,7 @@
         <v>572</v>
       </c>
       <c r="AE45" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.25">
@@ -20316,7 +20316,7 @@
         <v>572</v>
       </c>
       <c r="AE47" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
@@ -20403,7 +20403,7 @@
         <v>588</v>
       </c>
       <c r="AE48" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
@@ -20438,7 +20438,7 @@
         <v>11</v>
       </c>
       <c r="U49" s="49" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="V49" s="10">
         <v>50</v>
@@ -20450,7 +20450,7 @@
         <v>10</v>
       </c>
       <c r="Y49" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Z49" s="8" t="s">
         <v>572</v>
@@ -20459,10 +20459,10 @@
         <v>572</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG49" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
@@ -20521,7 +20521,7 @@
         <v>11</v>
       </c>
       <c r="U50" s="50" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="V50" s="10">
         <v>75</v>
@@ -20533,7 +20533,7 @@
         <v>10</v>
       </c>
       <c r="Y50" s="12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="Z50" s="8">
         <v>50</v>
@@ -20542,7 +20542,7 @@
         <v>572</v>
       </c>
       <c r="AE50" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
@@ -20679,7 +20679,7 @@
         <v>25</v>
       </c>
       <c r="AE52" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
@@ -20759,7 +20759,7 @@
         <v>572</v>
       </c>
       <c r="AE53" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
@@ -20839,7 +20839,7 @@
         <v>572</v>
       </c>
       <c r="AE54" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
@@ -21242,7 +21242,7 @@
         <v>572</v>
       </c>
       <c r="AE60" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
@@ -21410,7 +21410,7 @@
         <v>188</v>
       </c>
       <c r="V63" s="10" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="W63" s="9">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>20</v>
       </c>
       <c r="AE63" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
@@ -21515,7 +21515,7 @@
         <v>572</v>
       </c>
       <c r="AE64" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
@@ -21682,7 +21682,7 @@
         <v>572</v>
       </c>
       <c r="AE66" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
@@ -21951,13 +21951,13 @@
         <v>30</v>
       </c>
       <c r="J71" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K71" t="s">
         <v>11</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="M71" s="10">
         <v>75</v>
@@ -21969,7 +21969,7 @@
         <v>10</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="Q71" s="8">
         <v>50</v>
@@ -22009,7 +22009,7 @@
         <v>26</v>
       </c>
       <c r="AE71" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
@@ -22089,7 +22089,7 @@
         <v>572</v>
       </c>
       <c r="AE72" s="24" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
@@ -22160,7 +22160,7 @@
         <v>20</v>
       </c>
       <c r="Y73" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="Z73" s="8" t="s">
         <v>572</v>
@@ -22176,7 +22176,7 @@
         <v>27</v>
       </c>
       <c r="AE73" s="43" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
@@ -22239,10 +22239,10 @@
         <v>12</v>
       </c>
       <c r="AE74" s="43" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG74" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
@@ -22322,7 +22322,7 @@
         <v>572</v>
       </c>
       <c r="AE75" s="24" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
@@ -22402,7 +22402,7 @@
         <v>572</v>
       </c>
       <c r="AE76" s="43" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
@@ -22482,7 +22482,7 @@
         <v>572</v>
       </c>
       <c r="AE77" s="43" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
@@ -22569,10 +22569,10 @@
         <v>15</v>
       </c>
       <c r="AE78" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="AG78" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
@@ -22647,7 +22647,7 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H80" t="s">
         <v>572</v>
@@ -23627,7 +23627,7 @@
         <v>20</v>
       </c>
       <c r="P104" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="Q104" t="s">
         <v>572</v>
@@ -26272,13 +26272,13 @@
         <v>374</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1" t="s">
         <v>374</v>
       </c>
       <c r="I1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K1" t="s">
         <v>374</v>
@@ -26296,19 +26296,19 @@
         <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>352</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2" t="s">
         <v>352</v>
       </c>
       <c r="I2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K2" t="s">
         <v>352</v>
@@ -26331,19 +26331,19 @@
         <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E3" t="s">
         <v>353</v>
       </c>
       <c r="F3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H3" t="s">
         <v>353</v>
       </c>
       <c r="I3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K3" t="s">
         <v>353</v>
@@ -26352,7 +26352,7 @@
         <v>54</v>
       </c>
       <c r="N3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="O3" t="s">
         <v>54</v>
@@ -26369,13 +26369,13 @@
         <v>354</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H4" t="s">
         <v>354</v>
       </c>
       <c r="I4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K4" t="s">
         <v>354</v>
@@ -26401,13 +26401,13 @@
         <v>355</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H5" t="s">
         <v>355</v>
       </c>
       <c r="I5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K5" t="s">
         <v>355</v>
@@ -26416,7 +26416,7 @@
         <v>109</v>
       </c>
       <c r="N5" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="O5" t="s">
         <v>109</v>
@@ -26439,7 +26439,7 @@
         <v>356</v>
       </c>
       <c r="I6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K6" t="s">
         <v>356</v>
@@ -26459,13 +26459,13 @@
         <v>357</v>
       </c>
       <c r="F7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H7" t="s">
         <v>357</v>
       </c>
       <c r="I7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="K7" t="s">
         <v>357</v>
@@ -26491,13 +26491,13 @@
         <v>358</v>
       </c>
       <c r="F8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H8" t="s">
         <v>358</v>
       </c>
       <c r="I8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="K8" t="s">
         <v>358</v>
@@ -26517,13 +26517,13 @@
         <v>359</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>359</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K9" t="s">
         <v>359</v>
@@ -26549,13 +26549,13 @@
         <v>360</v>
       </c>
       <c r="F10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H10" t="s">
         <v>360</v>
       </c>
       <c r="I10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K10" t="s">
         <v>360</v>
@@ -26582,7 +26582,7 @@
         <v>361</v>
       </c>
       <c r="I11" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="K11" t="s">
         <v>361</v>
@@ -26603,13 +26603,13 @@
         <v>362</v>
       </c>
       <c r="F12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>362</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="K12" t="s">
         <v>362</v>
@@ -26630,13 +26630,13 @@
         <v>363</v>
       </c>
       <c r="F13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>363</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K13" t="s">
         <v>363</v>
@@ -26656,13 +26656,13 @@
         <v>364</v>
       </c>
       <c r="F14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H14" t="s">
         <v>364</v>
       </c>
       <c r="I14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K14" t="s">
         <v>364</v>
@@ -26683,13 +26683,13 @@
         <v>365</v>
       </c>
       <c r="F15" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H15" t="s">
         <v>365</v>
       </c>
       <c r="I15" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K15" t="s">
         <v>365</v>
@@ -26710,13 +26710,13 @@
         <v>366</v>
       </c>
       <c r="F16" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H16" t="s">
         <v>366</v>
       </c>
       <c r="I16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K16" t="s">
         <v>366</v>
@@ -26736,13 +26736,13 @@
         <v>367</v>
       </c>
       <c r="F17" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H17" t="s">
         <v>367</v>
       </c>
       <c r="I17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K17" t="s">
         <v>367</v>
@@ -26762,13 +26762,13 @@
         <v>368</v>
       </c>
       <c r="F18" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H18" t="s">
         <v>368</v>
       </c>
       <c r="I18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K18" t="s">
         <v>368</v>
@@ -26788,13 +26788,13 @@
         <v>369</v>
       </c>
       <c r="F19" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H19" t="s">
         <v>369</v>
       </c>
       <c r="I19" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K19" t="s">
         <v>369</v>
@@ -26814,13 +26814,13 @@
         <v>370</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H20" t="s">
         <v>370</v>
       </c>
       <c r="I20" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K20" t="s">
         <v>370</v>
@@ -26846,7 +26846,7 @@
         <v>371</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K21" t="s">
         <v>371</v>
@@ -26866,13 +26866,13 @@
         <v>372</v>
       </c>
       <c r="F22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H22" t="s">
         <v>372</v>
       </c>
       <c r="I22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K22" t="s">
         <v>372</v>
@@ -26892,7 +26892,7 @@
         <v>373</v>
       </c>
       <c r="F23" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H23" t="s">
         <v>373</v>
@@ -26918,7 +26918,7 @@
         <v>375</v>
       </c>
       <c r="F24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H24" t="s">
         <v>375</v>
@@ -26944,13 +26944,13 @@
         <v>376</v>
       </c>
       <c r="F25" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H25" t="s">
         <v>376</v>
       </c>
       <c r="I25" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K25" t="s">
         <v>376</v>
@@ -26970,13 +26970,13 @@
         <v>377</v>
       </c>
       <c r="F26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H26" t="s">
         <v>377</v>
       </c>
       <c r="I26" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K26" t="s">
         <v>377</v>
@@ -27002,7 +27002,7 @@
         <v>378</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K27" t="s">
         <v>378</v>
@@ -27022,13 +27022,13 @@
         <v>379</v>
       </c>
       <c r="F28" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H28" t="s">
         <v>379</v>
       </c>
       <c r="I28" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K28" t="s">
         <v>379</v>
@@ -27048,13 +27048,13 @@
         <v>380</v>
       </c>
       <c r="F29" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H29" t="s">
         <v>380</v>
       </c>
       <c r="I29" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="K29" t="s">
         <v>380</v>
@@ -27074,7 +27074,7 @@
         <v>381</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H30" t="s">
         <v>381</v>
@@ -27106,13 +27106,13 @@
         <v>382</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H31" t="s">
         <v>382</v>
       </c>
       <c r="I31" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K31" t="s">
         <v>382</v>
@@ -27132,13 +27132,13 @@
         <v>383</v>
       </c>
       <c r="F32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H32" t="s">
         <v>383</v>
       </c>
       <c r="I32" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K32" t="s">
         <v>383</v>
@@ -27158,13 +27158,13 @@
         <v>384</v>
       </c>
       <c r="F33" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H33" t="s">
         <v>384</v>
       </c>
       <c r="I33" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K33" t="s">
         <v>384</v>
@@ -27190,7 +27190,7 @@
         <v>385</v>
       </c>
       <c r="I34" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K34" t="s">
         <v>385</v>
@@ -27210,13 +27210,13 @@
         <v>386</v>
       </c>
       <c r="F35" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>386</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K35" t="s">
         <v>386</v>
@@ -27236,13 +27236,13 @@
         <v>387</v>
       </c>
       <c r="F36" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H36" t="s">
         <v>387</v>
       </c>
       <c r="I36" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="K36" t="s">
         <v>387</v>
@@ -27262,13 +27262,13 @@
         <v>388</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H37" t="s">
         <v>388</v>
       </c>
       <c r="I37" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K37" t="s">
         <v>388</v>
@@ -27294,7 +27294,7 @@
         <v>389</v>
       </c>
       <c r="I38" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="K38" t="s">
         <v>389</v>
@@ -27314,13 +27314,13 @@
         <v>390</v>
       </c>
       <c r="F39" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H39" t="s">
         <v>390</v>
       </c>
       <c r="I39" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K39" t="s">
         <v>390</v>
@@ -27340,13 +27340,13 @@
         <v>391</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H40" t="s">
         <v>391</v>
       </c>
       <c r="I40" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="K40" t="s">
         <v>391</v>
@@ -27372,13 +27372,13 @@
         <v>392</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H41" t="s">
         <v>392</v>
       </c>
       <c r="I41" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K41" t="s">
         <v>392</v>
@@ -27398,13 +27398,13 @@
         <v>393</v>
       </c>
       <c r="F42" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H42" t="s">
         <v>393</v>
       </c>
       <c r="I42" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K42" t="s">
         <v>393</v>
@@ -27424,13 +27424,13 @@
         <v>394</v>
       </c>
       <c r="F43" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>394</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K43" t="s">
         <v>394</v>
@@ -27450,13 +27450,13 @@
         <v>395</v>
       </c>
       <c r="F44" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H44" t="s">
         <v>395</v>
       </c>
       <c r="I44" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="K44" t="s">
         <v>395</v>
@@ -27476,7 +27476,7 @@
         <v>396</v>
       </c>
       <c r="F45" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H45" t="s">
         <v>396</v>
@@ -27508,7 +27508,7 @@
         <v>397</v>
       </c>
       <c r="I46" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K46" t="s">
         <v>397</v>
@@ -27528,13 +27528,13 @@
         <v>398</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H47" t="s">
         <v>398</v>
       </c>
       <c r="I47" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="K47" t="s">
         <v>398</v>
@@ -27554,13 +27554,13 @@
         <v>399</v>
       </c>
       <c r="F48" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H48" t="s">
         <v>399</v>
       </c>
       <c r="I48" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="K48" t="s">
         <v>399</v>
@@ -27580,13 +27580,13 @@
         <v>400</v>
       </c>
       <c r="F49" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>400</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K49" t="s">
         <v>400</v>
@@ -27606,13 +27606,13 @@
         <v>401</v>
       </c>
       <c r="F50" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>401</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="K50" t="s">
         <v>401</v>
@@ -28058,10 +28058,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="K78" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>214</v>
@@ -28069,19 +28069,19 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>120</v>
       </c>
       <c r="K79" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>264</v>
       </c>
       <c r="N79" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>264</v>
@@ -28089,13 +28089,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>29</v>
       </c>
       <c r="K80" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L80" s="44" t="s">
         <v>259</v>
@@ -28103,19 +28103,19 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B81" t="s">
         <v>54</v>
       </c>
       <c r="K81" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L81" s="46" t="s">
         <v>116</v>
       </c>
       <c r="N81" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>116</v>
@@ -28123,19 +28123,19 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>61</v>
       </c>
       <c r="H82" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I82" t="s">
         <v>263</v>
       </c>
       <c r="K82" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L82" s="48" t="s">
         <v>263</v>
@@ -28143,19 +28143,19 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B83" t="s">
         <v>109</v>
       </c>
       <c r="H83" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I83" t="s">
         <v>160</v>
       </c>
       <c r="K83" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L83" s="47" t="s">
         <v>160</v>
@@ -28163,19 +28163,19 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B84" t="s">
         <v>263</v>
       </c>
       <c r="K84" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>162</v>
       </c>
       <c r="N84" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="O84" s="7" t="s">
         <v>162</v>
@@ -28183,19 +28183,19 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B85" t="s">
         <v>160</v>
       </c>
       <c r="K85" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>90</v>
       </c>
       <c r="N85" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>90</v>

--- a/Notes/datamapping-MOVES.xlsx
+++ b/Notes/datamapping-MOVES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cygwin64\home\scrawford\silvermirror-local\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0160A33-6455-4F91-B8D7-CBC38E3A5BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662756A3-0B24-4731-933E-EC1B53B0ECAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{1982F562-5184-46C6-89BD-68E4E108BC42}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{1982F562-5184-46C6-89BD-68E4E108BC42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet6" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4768" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4769" uniqueCount="1398">
   <si>
     <t>bug</t>
   </si>
@@ -3705,9 +3705,6 @@
     <t>const FOCUS_BLAST</t>
   </si>
   <si>
-    <t>RESTORE</t>
-  </si>
-  <si>
     <t>EFFECT_SPEED_UP_2</t>
   </si>
   <si>
@@ -4234,13 +4231,16 @@
   </si>
   <si>
     <t>EFFECT_HEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORN_DRILL </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4352,6 +4352,14 @@
     <font>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4552,19 +4560,24 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="152">
+  <dxfs count="153">
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF00B050"/>
@@ -6326,7 +6339,7 @@
         <v>926</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -6373,22 +6386,22 @@
         <v>1212</v>
       </c>
       <c r="E5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G5" t="s">
         <v>1263</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>1264</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" t="s">
         <v>1266</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -6405,22 +6418,22 @@
         <v>479</v>
       </c>
       <c r="E6" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G6" t="s">
         <v>1263</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>1264</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -6485,26 +6498,26 @@
       <c r="B12" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>1093</v>
       </c>
       <c r="E12" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G12" t="s">
         <v>1263</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>1264</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J12" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -6532,22 +6545,22 @@
         <v>479</v>
       </c>
       <c r="E14" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G14" t="s">
         <v>1263</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>1264</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J14" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -6572,22 +6585,22 @@
         <v>1215</v>
       </c>
       <c r="E16" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G16" t="s">
         <v>1263</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>1264</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J16" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -6619,23 +6632,23 @@
       <c r="B19" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="53" t="s">
         <v>1094</v>
       </c>
       <c r="E19" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G19" t="s">
         <v>1263</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>1264</v>
       </c>
-      <c r="H19" t="s">
-        <v>1265</v>
-      </c>
       <c r="J19" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -6649,22 +6662,22 @@
         <v>1217</v>
       </c>
       <c r="E20" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G20" t="s">
         <v>1263</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>1264</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J20" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -6678,22 +6691,22 @@
         <v>1218</v>
       </c>
       <c r="E21" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G21" t="s">
         <v>1263</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>1264</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J21" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -6707,22 +6720,22 @@
         <v>1214</v>
       </c>
       <c r="E22" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G22" t="s">
         <v>1263</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>1264</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -6769,22 +6782,22 @@
         <v>1219</v>
       </c>
       <c r="E26" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G26" t="s">
         <v>1263</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>1264</v>
       </c>
-      <c r="H26" t="s">
-        <v>1265</v>
-      </c>
       <c r="I26" s="3" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="J26" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -6809,22 +6822,22 @@
         <v>1220</v>
       </c>
       <c r="E28" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G28" t="s">
         <v>1263</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>1264</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J28" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -6835,25 +6848,25 @@
         <v>1034</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E29" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G29" t="s">
         <v>1263</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>1264</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J29" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -6885,26 +6898,26 @@
       <c r="B32" s="3" t="s">
         <v>1037</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="53" t="s">
         <v>1092</v>
       </c>
       <c r="E32" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G32" t="s">
         <v>1263</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>1264</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J32" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -6926,25 +6939,25 @@
         <v>927</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E34" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G34" t="s">
         <v>1263</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>1264</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J34" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -6958,7 +6971,7 @@
         <v>948</v>
       </c>
       <c r="G35" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -6972,7 +6985,7 @@
         <v>949</v>
       </c>
       <c r="G36" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -7016,25 +7029,25 @@
         <v>953</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E40" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G40" t="s">
         <v>1263</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>1264</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J40" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -7062,22 +7075,22 @@
         <v>479</v>
       </c>
       <c r="E42" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F42" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G42" t="s">
         <v>1263</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>1264</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J42" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -7164,26 +7177,26 @@
       <c r="B50" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="C50" s="54" t="s">
+      <c r="C50" s="53" t="s">
         <v>1095</v>
       </c>
       <c r="E50" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G50" t="s">
         <v>1263</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>1264</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J50" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -7208,7 +7221,7 @@
         <v>959</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -7241,25 +7254,25 @@
         <v>962</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E55" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G55" t="s">
         <v>1263</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>1264</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J55" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -7401,23 +7414,23 @@
       <c r="B68" s="3" t="s">
         <v>969</v>
       </c>
-      <c r="C68" s="54" t="s">
+      <c r="C68" s="53" t="s">
         <v>1096</v>
       </c>
       <c r="E68" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F68" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G68" t="s">
         <v>1263</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>1264</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="J68" t="s">
         <v>58</v>
@@ -7453,22 +7466,22 @@
         <v>972</v>
       </c>
       <c r="C71" s="52" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E71" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F71" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G71" t="s">
         <v>1263</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>1264</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="J71" t="s">
         <v>42</v>
@@ -7738,7 +7751,7 @@
         <v>1060</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -7759,23 +7772,23 @@
       <c r="B97" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="C97" s="54" t="s">
+      <c r="C97" s="53" t="s">
         <v>1097</v>
       </c>
       <c r="E97" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F97" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G97" t="s">
         <v>1263</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>1264</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="J97" t="s">
         <v>89</v>
@@ -7844,25 +7857,25 @@
         <v>992</v>
       </c>
       <c r="C103" s="52" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E103" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G103" t="s">
         <v>1263</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>1264</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J103" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -7950,25 +7963,25 @@
         <v>1066</v>
       </c>
       <c r="C111" s="52" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E111" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F111" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G111" t="s">
         <v>1263</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>1264</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I111" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J111" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -7982,7 +7995,7 @@
         <v>1067</v>
       </c>
       <c r="G112" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
@@ -7996,7 +8009,7 @@
         <v>996</v>
       </c>
       <c r="G113" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
@@ -8073,25 +8086,25 @@
         <v>1003</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E120" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F120" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G120" t="s">
         <v>1263</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>1264</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J120" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8112,26 +8125,26 @@
       <c r="B122" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="C122" s="54" t="s">
+      <c r="C122" s="53" t="s">
         <v>1098</v>
       </c>
       <c r="E122" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F122" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G122" t="s">
         <v>1263</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>1264</v>
       </c>
-      <c r="H122" t="s">
-        <v>1265</v>
-      </c>
       <c r="I122" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J122" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8208,25 +8221,25 @@
         <v>1006</v>
       </c>
       <c r="C129" s="52" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E129" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F129" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G129" t="s">
         <v>1263</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>1264</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J129" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -8248,25 +8261,25 @@
         <v>1008</v>
       </c>
       <c r="C131" s="52" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E131" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F131" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G131" t="s">
         <v>1263</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>1264</v>
       </c>
-      <c r="H131" t="s">
+      <c r="I131" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J131" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -8276,26 +8289,26 @@
       <c r="B132" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="C132" s="54" t="s">
+      <c r="C132" s="53" t="s">
         <v>1099</v>
       </c>
       <c r="E132" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F132" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G132" t="s">
         <v>1263</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>1264</v>
       </c>
-      <c r="H132" t="s">
-        <v>1265</v>
-      </c>
       <c r="I132" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="J132" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -8306,25 +8319,25 @@
         <v>1010</v>
       </c>
       <c r="C133" s="52" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E133" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F133" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G133" t="s">
         <v>1263</v>
       </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>1264</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I133" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J133" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -8338,7 +8351,7 @@
         <v>1011</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8349,25 +8362,25 @@
         <v>1012</v>
       </c>
       <c r="C135" s="52" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E135" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F135" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G135" t="s">
         <v>1263</v>
       </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>1264</v>
       </c>
-      <c r="H135" t="s">
+      <c r="I135" s="56" t="s">
         <v>1265</v>
       </c>
-      <c r="I135" s="57" t="s">
-        <v>1266</v>
-      </c>
       <c r="J135" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8389,25 +8402,25 @@
         <v>1014</v>
       </c>
       <c r="C137" s="52" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E137" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F137" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G137" t="s">
         <v>1263</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>1264</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J137" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -8440,25 +8453,25 @@
         <v>1075</v>
       </c>
       <c r="C140" s="52" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E140" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F140" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G140" t="s">
         <v>1263</v>
       </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>1264</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I140" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J140" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -8469,25 +8482,25 @@
         <v>1076</v>
       </c>
       <c r="C141" s="52" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E141" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F141" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G141" t="s">
         <v>1263</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>1264</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I141" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J141" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8509,28 +8522,28 @@
         <v>1078</v>
       </c>
       <c r="C143" s="52" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E143" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F143" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G143" t="s">
         <v>1263</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>1264</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I143" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J143" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8544,7 +8557,7 @@
         <v>1079</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -8566,25 +8579,25 @@
         <v>1017</v>
       </c>
       <c r="C146" s="52" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E146" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G146" t="s">
         <v>1263</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>1264</v>
       </c>
-      <c r="H146" t="s">
-        <v>1265</v>
-      </c>
       <c r="I146" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J146" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -8628,22 +8641,22 @@
         <v>1021</v>
       </c>
       <c r="C150" s="52" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E150" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F150" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G150" t="s">
         <v>1263</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>1264</v>
       </c>
-      <c r="H150" t="s">
-        <v>1265</v>
-      </c>
       <c r="I150" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J150" t="s">
         <v>146</v>
@@ -8668,25 +8681,25 @@
         <v>1023</v>
       </c>
       <c r="C152" s="52" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E152" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F152" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G152" t="s">
         <v>1263</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>1264</v>
       </c>
-      <c r="H152" t="s">
-        <v>1265</v>
-      </c>
       <c r="I152" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J152" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -8708,25 +8721,25 @@
         <v>1025</v>
       </c>
       <c r="C154" s="52" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E154" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F154" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G154" t="s">
         <v>1263</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>1264</v>
       </c>
-      <c r="H154" t="s">
-        <v>1265</v>
-      </c>
       <c r="I154" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J154" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -8737,25 +8750,25 @@
         <v>1080</v>
       </c>
       <c r="C155" s="52" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E155" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F155" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G155" t="s">
         <v>1263</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>1264</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I155" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J155" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -8875,26 +8888,26 @@
       <c r="B166" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="C166" s="54" t="s">
+      <c r="C166" s="53" t="s">
         <v>1100</v>
       </c>
       <c r="E166" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G166" t="s">
         <v>1263</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>1264</v>
       </c>
-      <c r="H166" t="s">
-        <v>1265</v>
-      </c>
       <c r="I166" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J166" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -8916,25 +8929,25 @@
         <v>1102</v>
       </c>
       <c r="C168" s="52" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E168" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F168" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G168" t="s">
         <v>1263</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>1264</v>
       </c>
-      <c r="H168" t="s">
-        <v>1265</v>
-      </c>
       <c r="I168" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J168" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8956,62 +8969,62 @@
         <v>1104</v>
       </c>
       <c r="C170" s="52" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E170" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F170" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G170" t="s">
         <v>1263</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>1264</v>
       </c>
-      <c r="H170" t="s">
-        <v>1265</v>
-      </c>
       <c r="I170" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J170" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>1105</v>
       </c>
       <c r="C171" s="52" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E171" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F171" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G171" t="s">
         <v>1263</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>1264</v>
       </c>
-      <c r="H171" t="s">
-        <v>1265</v>
-      </c>
       <c r="I171" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J171" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B172" t="s">
         <v>1106</v>
@@ -9022,7 +9035,7 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B173" t="s">
         <v>1107</v>
@@ -9033,7 +9046,7 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B174" t="s">
         <v>1108</v>
@@ -9044,7 +9057,7 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B175" t="s">
         <v>1109</v>
@@ -9055,7 +9068,7 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B176" t="s">
         <v>1110</v>
@@ -9072,25 +9085,25 @@
         <v>1111</v>
       </c>
       <c r="C177" s="52" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E177" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F177" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G177" t="s">
         <v>1263</v>
       </c>
-      <c r="G177" t="s">
+      <c r="H177" t="s">
         <v>1264</v>
       </c>
-      <c r="H177" t="s">
-        <v>1265</v>
-      </c>
       <c r="I177" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J177" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -9112,25 +9125,25 @@
         <v>1113</v>
       </c>
       <c r="C179" s="52" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E179" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F179" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G179" t="s">
         <v>1263</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>1264</v>
       </c>
-      <c r="H179" t="s">
+      <c r="I179" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="I179" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="J179" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -9141,25 +9154,25 @@
         <v>1114</v>
       </c>
       <c r="C180" s="52" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E180" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F180" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G180" t="s">
         <v>1263</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>1264</v>
       </c>
-      <c r="H180" t="s">
-        <v>1265</v>
-      </c>
       <c r="I180" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J180" t="s">
         <v>61</v>
@@ -9173,28 +9186,28 @@
         <v>1115</v>
       </c>
       <c r="C181" s="52" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>479</v>
       </c>
       <c r="E181" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F181" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G181" t="s">
         <v>1263</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>1264</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>1265</v>
       </c>
-      <c r="I181" s="58" t="s">
-        <v>1266</v>
-      </c>
       <c r="J181" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -9260,25 +9273,25 @@
         <v>1121</v>
       </c>
       <c r="C187" s="52" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E187" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F187" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G187" t="s">
         <v>1263</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>1264</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>1265</v>
       </c>
-      <c r="I187" s="58" t="s">
-        <v>1266</v>
-      </c>
       <c r="J187" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -9316,7 +9329,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B191" t="s">
         <v>1125</v>
@@ -9327,7 +9340,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B192" t="s">
         <v>1126</v>
@@ -9338,7 +9351,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B193" t="s">
         <v>1127</v>
@@ -9349,7 +9362,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B194" t="s">
         <v>1128</v>
@@ -9360,7 +9373,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B195" t="s">
         <v>1129</v>
@@ -9371,7 +9384,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B196" t="s">
         <v>1130</v>
@@ -9382,7 +9395,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B197" t="s">
         <v>1131</v>
@@ -9393,62 +9406,62 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>1132</v>
       </c>
       <c r="C198" s="52" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E198" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F198" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G198" t="s">
         <v>1263</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>1264</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>1265</v>
       </c>
-      <c r="I198" s="58" t="s">
-        <v>1266</v>
-      </c>
       <c r="J198" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>1133</v>
       </c>
       <c r="C199" s="52" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E199" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F199" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G199" t="s">
         <v>1263</v>
       </c>
-      <c r="G199" t="s">
+      <c r="H199" t="s">
         <v>1264</v>
       </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>1265</v>
-      </c>
-      <c r="I199" s="58" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B200" t="s">
         <v>1134</v>
@@ -9459,7 +9472,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B201" t="s">
         <v>1135</v>
@@ -9470,7 +9483,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B202" t="s">
         <v>1136</v>
@@ -9481,7 +9494,7 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B203" t="s">
         <v>1137</v>
@@ -9492,7 +9505,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B204" t="s">
         <v>1138</v>
@@ -9503,7 +9516,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B205" t="s">
         <v>1139</v>
@@ -9514,7 +9527,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B206" t="s">
         <v>1140</v>
@@ -9525,7 +9538,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B207" t="s">
         <v>1141</v>
@@ -9536,7 +9549,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B208" t="s">
         <v>1142</v>
@@ -9547,36 +9560,36 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>1143</v>
       </c>
       <c r="C209" s="52" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E209" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F209" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G209" t="s">
         <v>1263</v>
       </c>
-      <c r="G209" t="s">
+      <c r="H209" t="s">
         <v>1264</v>
       </c>
-      <c r="H209" t="s">
-        <v>1265</v>
-      </c>
       <c r="I209" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J209" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B210" t="s">
         <v>1144</v>
@@ -9587,7 +9600,7 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B211" t="s">
         <v>1145</v>
@@ -9598,7 +9611,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B212" t="s">
         <v>1146</v>
@@ -9609,7 +9622,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B213" t="s">
         <v>1147</v>
@@ -9620,7 +9633,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B214" t="s">
         <v>1148</v>
@@ -9631,7 +9644,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B215" t="s">
         <v>1149</v>
@@ -9642,7 +9655,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B216" t="s">
         <v>1150</v>
@@ -9653,86 +9666,86 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>1151</v>
       </c>
       <c r="C217" s="52" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E217" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F217" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G217" t="s">
         <v>1263</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>1264</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>1265</v>
       </c>
-      <c r="I217" s="58" t="s">
-        <v>1266</v>
-      </c>
       <c r="J217" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>1152</v>
       </c>
       <c r="C218" s="52" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E218" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F218" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G218" t="s">
         <v>1263</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>1264</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>1265</v>
       </c>
-      <c r="I218" s="58" t="s">
-        <v>1266</v>
-      </c>
       <c r="J218" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>1153</v>
       </c>
       <c r="C219" s="52" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="E219" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F219" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G219" t="s">
         <v>1263</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>1264</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>1265</v>
-      </c>
-      <c r="I219" s="58" t="s">
-        <v>1266</v>
       </c>
       <c r="J219" t="s">
         <v>327</v>
@@ -9740,7 +9753,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B220" t="s">
         <v>1154</v>
@@ -9751,7 +9764,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B221" t="s">
         <v>1155</v>
@@ -9762,7 +9775,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B222" t="s">
         <v>1156</v>
@@ -9773,7 +9786,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B223" t="s">
         <v>1157</v>
@@ -9784,7 +9797,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B224" t="s">
         <v>1158</v>
@@ -9795,7 +9808,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B225" t="s">
         <v>1159</v>
@@ -9806,7 +9819,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B226" t="s">
         <v>1160</v>
@@ -9817,7 +9830,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B227" t="s">
         <v>1161</v>
@@ -9828,7 +9841,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B228" t="s">
         <v>1162</v>
@@ -9839,7 +9852,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B229" t="s">
         <v>1163</v>
@@ -9850,7 +9863,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B230" t="s">
         <v>1164</v>
@@ -9861,7 +9874,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B231" t="s">
         <v>1165</v>
@@ -9872,7 +9885,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B232" t="s">
         <v>1166</v>
@@ -9883,7 +9896,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B233" t="s">
         <v>1167</v>
@@ -9894,36 +9907,36 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>1168</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E234" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F234" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G234" t="s">
         <v>1263</v>
       </c>
-      <c r="G234" t="s">
+      <c r="H234" t="s">
         <v>1264</v>
       </c>
-      <c r="H234" t="s">
-        <v>1265</v>
-      </c>
       <c r="I234" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J234" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B235" t="s">
         <v>1169</v>
@@ -9934,7 +9947,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B236" t="s">
         <v>1170</v>
@@ -9945,7 +9958,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B237" t="s">
         <v>1171</v>
@@ -9956,7 +9969,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B238" t="s">
         <v>1172</v>
@@ -9967,7 +9980,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B239" t="s">
         <v>1173</v>
@@ -9978,7 +9991,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B240" t="s">
         <v>1174</v>
@@ -9989,7 +10002,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B241" t="s">
         <v>1175</v>
@@ -10000,7 +10013,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B242" t="s">
         <v>1176</v>
@@ -10011,7 +10024,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B243" t="s">
         <v>1177</v>
@@ -10022,7 +10035,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B244" t="s">
         <v>1178</v>
@@ -10033,28 +10046,28 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>1192</v>
       </c>
-      <c r="C245" s="54" t="s">
+      <c r="C245" s="53" t="s">
         <v>1179</v>
       </c>
       <c r="E245" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F245" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G245" t="s">
         <v>1263</v>
       </c>
-      <c r="G245" t="s">
+      <c r="H245" t="s">
         <v>1264</v>
       </c>
-      <c r="H245" t="s">
-        <v>1265</v>
-      </c>
       <c r="I245" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J245" t="s">
         <v>89</v>
@@ -10062,7 +10075,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B246" t="s">
         <v>1180</v>
@@ -10073,7 +10086,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B247" t="s">
         <v>1181</v>
@@ -10084,7 +10097,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="B248" t="s">
         <v>1182</v>
@@ -10095,7 +10108,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B249" t="s">
         <v>1183</v>
@@ -10106,15 +10119,15 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>1371</v>
-      </c>
-      <c r="B250" s="55" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B250" s="54" t="s">
         <v>1184</v>
       </c>
-      <c r="C250" s="56" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D250" s="55"/>
+      <c r="C250" s="55" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D250" s="54"/>
       <c r="E250" s="5"/>
       <c r="J250" t="s">
         <v>19</v>
@@ -10122,7 +10135,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B251" t="s">
         <v>1185</v>
@@ -10133,111 +10146,111 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>1186</v>
       </c>
       <c r="C252" s="52" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E252" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F252" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G252" t="s">
         <v>1263</v>
       </c>
-      <c r="G252" t="s">
+      <c r="H252" t="s">
         <v>1264</v>
       </c>
-      <c r="H252" t="s">
-        <v>1265</v>
-      </c>
       <c r="I252" s="4" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="J252" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C253" s="54" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C253" s="53" t="s">
         <v>1188</v>
       </c>
       <c r="E253" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F253" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G253" t="s">
         <v>1263</v>
       </c>
-      <c r="G253" t="s">
+      <c r="H253" t="s">
         <v>1264</v>
       </c>
-      <c r="H253" t="s">
-        <v>1265</v>
-      </c>
       <c r="J253" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C254" s="54" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C254" s="53" t="s">
         <v>1189</v>
       </c>
       <c r="E254" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F254" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G254" t="s">
         <v>1263</v>
       </c>
-      <c r="G254" t="s">
+      <c r="H254" t="s">
         <v>1264</v>
       </c>
-      <c r="H254" t="s">
-        <v>1265</v>
-      </c>
       <c r="J254" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C255" s="54" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C255" s="53" t="s">
         <v>1187</v>
       </c>
       <c r="E255" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="F255" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G255" t="s">
         <v>1263</v>
       </c>
-      <c r="G255" t="s">
+      <c r="H255" t="s">
         <v>1264</v>
       </c>
-      <c r="H255" t="s">
-        <v>1265</v>
-      </c>
       <c r="J255" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C256" t="s">
         <v>1091</v>
       </c>
       <c r="G256" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
   </sheetData>
@@ -14906,9 +14919,7 @@
       <c r="D153" t="s">
         <v>113</v>
       </c>
-      <c r="H153" s="53" t="s">
-        <v>1221</v>
-      </c>
+      <c r="H153" s="58"/>
       <c r="J153" t="s">
         <v>113</v>
       </c>
@@ -16880,44 +16891,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576 J1:J1048576">
-    <cfRule type="duplicateValues" dxfId="151" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D256 A260:A1048576 D314:D1048576 A1:A258">
-    <cfRule type="duplicateValues" dxfId="150" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D256 D314:D1048576 F1:F170 F172:F1048576 H103">
-    <cfRule type="duplicateValues" dxfId="149" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D256 D314:D1048576">
-    <cfRule type="duplicateValues" dxfId="148" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="130"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D260:D313 D257:D258">
-    <cfRule type="duplicateValues" dxfId="147" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D305:D310 D283 D287 D296:D300 D302:D303 D294 D289 D278 D273 D268 D260:D262">
-    <cfRule type="duplicateValues" dxfId="146" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:E170 D172:E256 D314:E1048576 E257:E313 D171 F171">
-    <cfRule type="duplicateValues" dxfId="145" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:E256 D314:E1048576 E257:E313">
-    <cfRule type="duplicateValues" dxfId="144" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576 A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="143" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K17 J19:K1048576 J18 L172 L211">
-    <cfRule type="duplicateValues" dxfId="142" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53:O1048576 O1:O6 O8:O51">
-    <cfRule type="duplicateValues" dxfId="140" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O53:O1048576 O1:O51">
-    <cfRule type="duplicateValues" dxfId="139" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U5 U9:U1048576">
-    <cfRule type="duplicateValues" dxfId="138" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18113,7 +18124,7 @@
         <v>572</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -18828,7 +18839,7 @@
         <v>572</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AG26" s="4" t="s">
         <v>606</v>
@@ -19181,7 +19192,7 @@
         <v>10</v>
       </c>
       <c r="Y31" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="Z31" s="8" t="s">
         <v>572</v>
@@ -19190,7 +19201,7 @@
         <v>572</v>
       </c>
       <c r="AE31" s="4" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
@@ -22569,7 +22580,7 @@
         <v>15</v>
       </c>
       <c r="AE78" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="AG78" t="s">
         <v>656</v>
@@ -23992,343 +24003,343 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C8:C14">
-    <cfRule type="duplicateValues" dxfId="137" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:C18">
-    <cfRule type="duplicateValues" dxfId="135" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="92"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C22">
-    <cfRule type="duplicateValues" dxfId="134" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C23:C31">
-    <cfRule type="duplicateValues" dxfId="132" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="93"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:C37">
-    <cfRule type="duplicateValues" dxfId="131" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38:C42">
-    <cfRule type="duplicateValues" dxfId="130" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C47">
-    <cfRule type="duplicateValues" dxfId="129" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48:C53">
-    <cfRule type="duplicateValues" dxfId="127" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50:C51">
-    <cfRule type="duplicateValues" dxfId="126" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55:C58">
-    <cfRule type="duplicateValues" dxfId="125" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C59:C62">
-    <cfRule type="duplicateValues" dxfId="124" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C63:C70">
-    <cfRule type="duplicateValues" dxfId="122" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="94"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C71:C76">
-    <cfRule type="duplicateValues" dxfId="121" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C77:C81">
-    <cfRule type="duplicateValues" dxfId="120" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C86">
-    <cfRule type="duplicateValues" dxfId="119" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C87:C94">
-    <cfRule type="duplicateValues" dxfId="118" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C95:C98">
-    <cfRule type="duplicateValues" dxfId="117" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C100:C108">
-    <cfRule type="duplicateValues" dxfId="116" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C110:C112">
-    <cfRule type="duplicateValues" dxfId="115" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C116:C1048576 C1:C7">
-    <cfRule type="duplicateValues" dxfId="114" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="91"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576 U1:U1048576">
-    <cfRule type="duplicateValues" dxfId="113" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:L12">
-    <cfRule type="duplicateValues" dxfId="112" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="627"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L14:L16">
-    <cfRule type="duplicateValues" dxfId="111" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L18:L21">
-    <cfRule type="duplicateValues" dxfId="110" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L23:L30">
-    <cfRule type="duplicateValues" dxfId="108" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="515"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:L36">
-    <cfRule type="duplicateValues" dxfId="107" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L38:L41">
-    <cfRule type="duplicateValues" dxfId="106" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="507"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L44:L48">
-    <cfRule type="duplicateValues" dxfId="105" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L50:L51">
-    <cfRule type="duplicateValues" dxfId="103" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L50:L53 L55:L56">
-    <cfRule type="duplicateValues" dxfId="102" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="646"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58:L61">
-    <cfRule type="duplicateValues" dxfId="101" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="103"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L63:L66">
-    <cfRule type="duplicateValues" dxfId="100" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L68:L70 L72:L73">
-    <cfRule type="duplicateValues" dxfId="98" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="797"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L71">
-    <cfRule type="duplicateValues" dxfId="97" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L75:L80">
-    <cfRule type="duplicateValues" dxfId="96" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="647"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L81:L83">
-    <cfRule type="duplicateValues" dxfId="95" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="499"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L85:L88">
-    <cfRule type="duplicateValues" dxfId="94" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="495"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L90:L95">
-    <cfRule type="duplicateValues" dxfId="93" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="491"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L97:L100">
-    <cfRule type="duplicateValues" dxfId="92" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L103">
-    <cfRule type="duplicateValues" dxfId="91" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L105">
-    <cfRule type="duplicateValues" dxfId="90" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="531"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L107">
-    <cfRule type="duplicateValues" dxfId="89" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="543"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L109">
-    <cfRule type="duplicateValues" dxfId="88" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="539"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L111">
-    <cfRule type="duplicateValues" dxfId="87" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112 L108">
-    <cfRule type="duplicateValues" dxfId="86" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L113 L104">
-    <cfRule type="duplicateValues" dxfId="85" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L114:L115 L102">
-    <cfRule type="duplicateValues" dxfId="84" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="570"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117">
-    <cfRule type="duplicateValues" dxfId="83" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L118 L110 L106">
-    <cfRule type="duplicateValues" dxfId="82" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L125:L1048576 L101 L1:L7">
-    <cfRule type="duplicateValues" dxfId="81" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="691"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U16 U18:U19 L1:L1048576 U21:U41 U43:U1048576">
-    <cfRule type="duplicateValues" dxfId="80" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="794"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="duplicateValues" dxfId="79" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3">
-    <cfRule type="duplicateValues" dxfId="78" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4">
-    <cfRule type="duplicateValues" dxfId="77" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
-    <cfRule type="duplicateValues" dxfId="76" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U7">
-    <cfRule type="duplicateValues" dxfId="75" priority="766"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U8">
-    <cfRule type="duplicateValues" dxfId="74" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:U11">
-    <cfRule type="duplicateValues" dxfId="73" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U13">
-    <cfRule type="duplicateValues" dxfId="72" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U14:U15">
-    <cfRule type="duplicateValues" dxfId="70" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U16">
-    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U18">
-    <cfRule type="duplicateValues" dxfId="67" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U19">
-    <cfRule type="duplicateValues" dxfId="66" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1013"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U22">
-    <cfRule type="duplicateValues" dxfId="65" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U23">
-    <cfRule type="duplicateValues" dxfId="64" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U25">
-    <cfRule type="duplicateValues" dxfId="63" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U26">
-    <cfRule type="duplicateValues" dxfId="62" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U29">
-    <cfRule type="duplicateValues" dxfId="61" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U30">
-    <cfRule type="duplicateValues" dxfId="59" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U31">
-    <cfRule type="duplicateValues" dxfId="57" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33">
-    <cfRule type="duplicateValues" dxfId="55" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34">
-    <cfRule type="duplicateValues" dxfId="53" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35">
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U36">
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U37">
-    <cfRule type="duplicateValues" dxfId="49" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U39:U41">
-    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U43:U45">
-    <cfRule type="duplicateValues" dxfId="47" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U47">
-    <cfRule type="duplicateValues" dxfId="45" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U48:U50">
-    <cfRule type="duplicateValues" dxfId="44" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="1003"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U52">
-    <cfRule type="duplicateValues" dxfId="43" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U53">
-    <cfRule type="duplicateValues" dxfId="42" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U54">
-    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U56:U57">
-    <cfRule type="duplicateValues" dxfId="40" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="660"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U59:U61">
-    <cfRule type="duplicateValues" dxfId="39" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="673"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U63">
-    <cfRule type="duplicateValues" dxfId="38" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U64">
-    <cfRule type="duplicateValues" dxfId="37" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U65">
-    <cfRule type="duplicateValues" dxfId="36" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U66">
-    <cfRule type="duplicateValues" dxfId="35" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U68:U69">
-    <cfRule type="duplicateValues" dxfId="34" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U71">
-    <cfRule type="duplicateValues" dxfId="33" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U72">
-    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U73">
-    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U74">
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U75">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U76">
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U77">
-    <cfRule type="duplicateValues" dxfId="27" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U78">
-    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U79">
-    <cfRule type="duplicateValues" dxfId="25" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U81">
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U83:U86 U67 U32 U1 U38 U46 U51 U55 U70 U93:U1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="756"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U90">
-    <cfRule type="duplicateValues" dxfId="22" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U92">
-    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE72">
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE73">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE74">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE75">
-    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE76">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE77">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -26196,44 +26207,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C35 M1:M1048576 C1:C17 C24:C25 C20 C30 C43:C1048576 C37:C38">
-    <cfRule type="duplicateValues" dxfId="8" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C35 M1:M1048576 C1:C18 C24:C25 C20 C30 C43:C1048576 C37:C38">
-    <cfRule type="duplicateValues" dxfId="7" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="709"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C1048576 C1:C31 C33:C38">
-    <cfRule type="duplicateValues" dxfId="6" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="734"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43:C1048576 M1:M1048576 C1:C31 C33:C38">
-    <cfRule type="duplicateValues" dxfId="5" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="738"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576 A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576 C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26904,7 +26915,7 @@
         <v>373</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -27409,8 +27420,8 @@
       <c r="K42" t="s">
         <v>393</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>161</v>
+      <c r="L42" s="44" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -27513,8 +27524,14 @@
       <c r="K46" t="s">
         <v>397</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>272</v>
+      <c r="L46" s="57" t="s">
+        <v>1397</v>
+      </c>
+      <c r="N46" t="s">
+        <v>397</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -27540,7 +27557,7 @@
         <v>398</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -27751,7 +27768,7 @@
         <v>409</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>209</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -27925,11 +27942,11 @@
       <c r="B69" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="L69" s="44" t="s">
-        <v>244</v>
+      <c r="L69" s="7" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -28218,7 +28235,10 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="L1:L1048576 I91:I1048576 I1:I88 F1:F1048576">
+  <conditionalFormatting sqref="I91:I1048576 I1:I88 F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L68 L70:L1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
